--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776-26271\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31D77DC6-6DFE-48E0-A9DC-95736FE82147}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B9A733B-B549-47A5-8DCE-EA05C58CC23B}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -210,9 +210,6 @@
     <t>Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">Today the classes are good.And felt tired </t>
-  </si>
-  <si>
     <t>Neutral</t>
   </si>
   <si>
@@ -220,6 +217,15 @@
   </si>
   <si>
     <t>Tired</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Happy</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
   </si>
 </sst>
 </file>
@@ -229,7 +235,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -377,9 +383,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,186 +664,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="105" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.1">
+    <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.5">
+    <row r="2" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -848,8 +854,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="14.45"/>
+  <dimension ref="A1:N400"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
@@ -862,77 +868,77 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-    </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+    </row>
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
       <c r="E2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="15">
         <v>12605718</v>
       </c>
-      <c r="G2" s="14"/>
-    </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1">
+      <c r="G2" s="15"/>
+    </row>
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
       <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="14"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="15" t="s">
+      <c r="G3" s="15"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-    </row>
-    <row r="5" spans="1:14" ht="42">
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+    </row>
+    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>39</v>
       </c>
@@ -976,7 +982,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="30.75">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46251</v>
       </c>
@@ -1019,10 +1025,10 @@
         <v>55</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="15">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>46252</v>
       </c>
@@ -1056,19 +1062,19 @@
         <v>150</v>
       </c>
       <c r="K7" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7" s="11" t="s">
+      <c r="N7" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="N7" s="12" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="15">
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>46253</v>
       </c>
@@ -1102,7 +1108,7 @@
         <v>148</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L8" s="11" t="s">
         <v>54</v>
@@ -1110,75 +1116,149 @@
       <c r="M8" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="N8" s="12"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10" t="str">
+      <c r="N8" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B9" s="9">
+        <v>420</v>
+      </c>
+      <c r="C9" s="9">
+        <v>120</v>
+      </c>
+      <c r="D9" s="9">
+        <v>100</v>
+      </c>
+      <c r="E9" s="9">
+        <v>20</v>
+      </c>
+      <c r="F9" s="9">
+        <v>150</v>
+      </c>
+      <c r="G9" s="9">
+        <v>3</v>
+      </c>
+      <c r="H9" s="9">
+        <v>200</v>
+      </c>
+      <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="10" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10" t="str">
+        <v>430</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="9">
+        <v>480</v>
+      </c>
+      <c r="C10" s="9">
+        <v>120</v>
+      </c>
+      <c r="D10" s="9">
+        <v>120</v>
+      </c>
+      <c r="E10" s="9">
+        <v>30</v>
+      </c>
+      <c r="F10" s="9">
+        <v>200</v>
+      </c>
+      <c r="G10" s="9">
+        <v>4</v>
+      </c>
+      <c r="H10" s="9">
+        <v>240</v>
+      </c>
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="10" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="12"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10" t="str">
+        <v>250</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B11" s="9">
+        <v>480</v>
+      </c>
+      <c r="C11" s="9">
+        <v>100</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>300</v>
+      </c>
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
+        <v>880</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="12"/>
-    </row>
-    <row r="12" spans="1:14">
+        <v>560</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
@@ -1200,7 +1280,7 @@
       <c r="M12" s="11"/>
       <c r="N12" s="12"/>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
@@ -1222,7 +1302,7 @@
       <c r="M13" s="11"/>
       <c r="N13" s="12"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1244,7 +1324,7 @@
       <c r="M14" s="11"/>
       <c r="N14" s="12"/>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1266,7 +1346,7 @@
       <c r="M15" s="11"/>
       <c r="N15" s="12"/>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1288,7 +1368,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="12"/>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -1310,7 +1390,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="12"/>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -1332,7 +1412,7 @@
       <c r="M18" s="11"/>
       <c r="N18" s="12"/>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -1354,7 +1434,7 @@
       <c r="M19" s="11"/>
       <c r="N19" s="12"/>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -1376,7 +1456,7 @@
       <c r="M20" s="11"/>
       <c r="N20" s="12"/>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -1398,7 +1478,7 @@
       <c r="M21" s="11"/>
       <c r="N21" s="12"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -1420,7 +1500,7 @@
       <c r="M22" s="11"/>
       <c r="N22" s="12"/>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -1442,7 +1522,7 @@
       <c r="M23" s="11"/>
       <c r="N23" s="12"/>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -1464,7 +1544,7 @@
       <c r="M24" s="11"/>
       <c r="N24" s="12"/>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1486,7 +1566,7 @@
       <c r="M25" s="11"/>
       <c r="N25" s="12"/>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
@@ -1508,7 +1588,7 @@
       <c r="M26" s="11"/>
       <c r="N26" s="12"/>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -1530,7 +1610,7 @@
       <c r="M27" s="11"/>
       <c r="N27" s="12"/>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -1552,7 +1632,7 @@
       <c r="M28" s="11"/>
       <c r="N28" s="12"/>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -1574,7 +1654,7 @@
       <c r="M29" s="11"/>
       <c r="N29" s="12"/>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -1596,7 +1676,7 @@
       <c r="M30" s="11"/>
       <c r="N30" s="12"/>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -1618,7 +1698,7 @@
       <c r="M31" s="11"/>
       <c r="N31" s="12"/>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -1640,7 +1720,7 @@
       <c r="M32" s="11"/>
       <c r="N32" s="12"/>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -1662,7 +1742,7 @@
       <c r="M33" s="11"/>
       <c r="N33" s="12"/>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -1684,7 +1764,7 @@
       <c r="M34" s="11"/>
       <c r="N34" s="12"/>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -1706,7 +1786,7 @@
       <c r="M35" s="11"/>
       <c r="N35" s="12"/>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -1728,7 +1808,7 @@
       <c r="M36" s="11"/>
       <c r="N36" s="12"/>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -1750,7 +1830,7 @@
       <c r="M37" s="11"/>
       <c r="N37" s="12"/>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -1772,7 +1852,7 @@
       <c r="M38" s="11"/>
       <c r="N38" s="12"/>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -1794,7 +1874,7 @@
       <c r="M39" s="11"/>
       <c r="N39" s="12"/>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -1816,7 +1896,7 @@
       <c r="M40" s="11"/>
       <c r="N40" s="12"/>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -1838,7 +1918,7 @@
       <c r="M41" s="11"/>
       <c r="N41" s="12"/>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1860,7 +1940,7 @@
       <c r="M42" s="11"/>
       <c r="N42" s="12"/>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1882,7 +1962,7 @@
       <c r="M43" s="11"/>
       <c r="N43" s="12"/>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -1904,7 +1984,7 @@
       <c r="M44" s="11"/>
       <c r="N44" s="12"/>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -1926,7 +2006,7 @@
       <c r="M45" s="11"/>
       <c r="N45" s="12"/>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1948,7 +2028,7 @@
       <c r="M46" s="11"/>
       <c r="N46" s="12"/>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1970,7 +2050,7 @@
       <c r="M47" s="11"/>
       <c r="N47" s="12"/>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -1992,7 +2072,7 @@
       <c r="M48" s="11"/>
       <c r="N48" s="12"/>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -2014,7 +2094,7 @@
       <c r="M49" s="11"/>
       <c r="N49" s="12"/>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -2036,7 +2116,7 @@
       <c r="M50" s="11"/>
       <c r="N50" s="12"/>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
@@ -2058,7 +2138,7 @@
       <c r="M51" s="11"/>
       <c r="N51" s="12"/>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="9"/>
       <c r="C52" s="9"/>
@@ -2080,7 +2160,7 @@
       <c r="M52" s="11"/>
       <c r="N52" s="12"/>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
@@ -2102,7 +2182,7 @@
       <c r="M53" s="11"/>
       <c r="N53" s="12"/>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="9"/>
       <c r="C54" s="9"/>
@@ -2124,7 +2204,7 @@
       <c r="M54" s="11"/>
       <c r="N54" s="12"/>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
       <c r="B55" s="9"/>
       <c r="C55" s="9"/>
@@ -2146,7 +2226,7 @@
       <c r="M55" s="11"/>
       <c r="N55" s="12"/>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="9"/>
       <c r="C56" s="9"/>
@@ -2168,7 +2248,7 @@
       <c r="M56" s="11"/>
       <c r="N56" s="12"/>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
       <c r="B57" s="9"/>
       <c r="C57" s="9"/>
@@ -2190,7 +2270,7 @@
       <c r="M57" s="11"/>
       <c r="N57" s="12"/>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -2212,7 +2292,7 @@
       <c r="M58" s="11"/>
       <c r="N58" s="12"/>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="8"/>
       <c r="B59" s="9"/>
       <c r="C59" s="9"/>
@@ -2234,7 +2314,7 @@
       <c r="M59" s="11"/>
       <c r="N59" s="12"/>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
       <c r="B60" s="9"/>
       <c r="C60" s="9"/>
@@ -2256,7 +2336,7 @@
       <c r="M60" s="11"/>
       <c r="N60" s="12"/>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>
       <c r="B61" s="9"/>
       <c r="C61" s="9"/>
@@ -2278,7 +2358,7 @@
       <c r="M61" s="11"/>
       <c r="N61" s="12"/>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
       <c r="B62" s="9"/>
       <c r="C62" s="9"/>
@@ -2300,7 +2380,7 @@
       <c r="M62" s="11"/>
       <c r="N62" s="12"/>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
       <c r="B63" s="9"/>
       <c r="C63" s="9"/>
@@ -2322,7 +2402,7 @@
       <c r="M63" s="11"/>
       <c r="N63" s="12"/>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
       <c r="B64" s="9"/>
       <c r="C64" s="9"/>
@@ -2344,7 +2424,7 @@
       <c r="M64" s="11"/>
       <c r="N64" s="12"/>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="9"/>
       <c r="C65" s="9"/>
@@ -2366,7 +2446,7 @@
       <c r="M65" s="11"/>
       <c r="N65" s="12"/>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
@@ -2388,7 +2468,7 @@
       <c r="M66" s="11"/>
       <c r="N66" s="12"/>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
@@ -2410,7 +2490,7 @@
       <c r="M67" s="11"/>
       <c r="N67" s="12"/>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
@@ -2432,7 +2512,7 @@
       <c r="M68" s="11"/>
       <c r="N68" s="12"/>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
@@ -2454,7 +2534,7 @@
       <c r="M69" s="11"/>
       <c r="N69" s="12"/>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
@@ -2476,7 +2556,7 @@
       <c r="M70" s="11"/>
       <c r="N70" s="12"/>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
@@ -2498,7 +2578,7 @@
       <c r="M71" s="11"/>
       <c r="N71" s="12"/>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
@@ -2520,7 +2600,7 @@
       <c r="M72" s="11"/>
       <c r="N72" s="12"/>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
@@ -2542,7 +2622,7 @@
       <c r="M73" s="11"/>
       <c r="N73" s="12"/>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
@@ -2564,7 +2644,7 @@
       <c r="M74" s="11"/>
       <c r="N74" s="12"/>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
@@ -2586,7 +2666,7 @@
       <c r="M75" s="11"/>
       <c r="N75" s="12"/>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
@@ -2608,7 +2688,7 @@
       <c r="M76" s="11"/>
       <c r="N76" s="12"/>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
@@ -2630,7 +2710,7 @@
       <c r="M77" s="11"/>
       <c r="N77" s="12"/>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
@@ -2652,7 +2732,7 @@
       <c r="M78" s="11"/>
       <c r="N78" s="12"/>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
@@ -2674,7 +2754,7 @@
       <c r="M79" s="11"/>
       <c r="N79" s="12"/>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
@@ -2696,7 +2776,7 @@
       <c r="M80" s="11"/>
       <c r="N80" s="12"/>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="8"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
@@ -2718,7 +2798,7 @@
       <c r="M81" s="11"/>
       <c r="N81" s="12"/>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
@@ -2740,7 +2820,7 @@
       <c r="M82" s="11"/>
       <c r="N82" s="12"/>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="8"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
@@ -2762,7 +2842,7 @@
       <c r="M83" s="11"/>
       <c r="N83" s="12"/>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="8"/>
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
@@ -2784,7 +2864,7 @@
       <c r="M84" s="11"/>
       <c r="N84" s="12"/>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="8"/>
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
@@ -2806,7 +2886,7 @@
       <c r="M85" s="11"/>
       <c r="N85" s="12"/>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="8"/>
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
@@ -2828,7 +2908,7 @@
       <c r="M86" s="11"/>
       <c r="N86" s="12"/>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="8"/>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
@@ -2850,7 +2930,7 @@
       <c r="M87" s="11"/>
       <c r="N87" s="12"/>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="8"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
@@ -2872,7 +2952,7 @@
       <c r="M88" s="11"/>
       <c r="N88" s="12"/>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="8"/>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
@@ -2894,7 +2974,7 @@
       <c r="M89" s="11"/>
       <c r="N89" s="12"/>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="8"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
@@ -2916,7 +2996,7 @@
       <c r="M90" s="11"/>
       <c r="N90" s="12"/>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="8"/>
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
@@ -2938,7 +3018,7 @@
       <c r="M91" s="11"/>
       <c r="N91" s="12"/>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="8"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
@@ -2960,7 +3040,7 @@
       <c r="M92" s="11"/>
       <c r="N92" s="12"/>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="8"/>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
@@ -2982,7 +3062,7 @@
       <c r="M93" s="11"/>
       <c r="N93" s="12"/>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="8"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
@@ -3004,7 +3084,7 @@
       <c r="M94" s="11"/>
       <c r="N94" s="12"/>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="8"/>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
@@ -3026,7 +3106,7 @@
       <c r="M95" s="11"/>
       <c r="N95" s="12"/>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="8"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
@@ -3048,7 +3128,7 @@
       <c r="M96" s="11"/>
       <c r="N96" s="12"/>
     </row>
-    <row r="97" spans="1:14">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="8"/>
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
@@ -3070,7 +3150,7 @@
       <c r="M97" s="11"/>
       <c r="N97" s="12"/>
     </row>
-    <row r="98" spans="1:14">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="8"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
@@ -3092,7 +3172,7 @@
       <c r="M98" s="11"/>
       <c r="N98" s="12"/>
     </row>
-    <row r="99" spans="1:14">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="8"/>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
@@ -3114,7 +3194,7 @@
       <c r="M99" s="11"/>
       <c r="N99" s="12"/>
     </row>
-    <row r="100" spans="1:14">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="8"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
@@ -3136,7 +3216,7 @@
       <c r="M100" s="11"/>
       <c r="N100" s="12"/>
     </row>
-    <row r="101" spans="1:14">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="8"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
@@ -3158,7 +3238,7 @@
       <c r="M101" s="11"/>
       <c r="N101" s="12"/>
     </row>
-    <row r="102" spans="1:14">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="8"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
@@ -3180,7 +3260,7 @@
       <c r="M102" s="11"/>
       <c r="N102" s="12"/>
     </row>
-    <row r="103" spans="1:14">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="8"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
@@ -3202,7 +3282,7 @@
       <c r="M103" s="11"/>
       <c r="N103" s="12"/>
     </row>
-    <row r="104" spans="1:14">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="8"/>
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
@@ -3224,7 +3304,7 @@
       <c r="M104" s="11"/>
       <c r="N104" s="12"/>
     </row>
-    <row r="105" spans="1:14">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="8"/>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
@@ -3246,7 +3326,7 @@
       <c r="M105" s="11"/>
       <c r="N105" s="12"/>
     </row>
-    <row r="106" spans="1:14">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="8"/>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
@@ -3268,7 +3348,7 @@
       <c r="M106" s="11"/>
       <c r="N106" s="12"/>
     </row>
-    <row r="107" spans="1:14">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="8"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
@@ -3290,7 +3370,7 @@
       <c r="M107" s="11"/>
       <c r="N107" s="12"/>
     </row>
-    <row r="108" spans="1:14">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="8"/>
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
@@ -3312,7 +3392,7 @@
       <c r="M108" s="11"/>
       <c r="N108" s="12"/>
     </row>
-    <row r="109" spans="1:14">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="8"/>
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
@@ -3334,7 +3414,7 @@
       <c r="M109" s="11"/>
       <c r="N109" s="12"/>
     </row>
-    <row r="110" spans="1:14">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="8"/>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
@@ -3356,7 +3436,7 @@
       <c r="M110" s="11"/>
       <c r="N110" s="12"/>
     </row>
-    <row r="111" spans="1:14">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="8"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
@@ -3378,7 +3458,7 @@
       <c r="M111" s="11"/>
       <c r="N111" s="12"/>
     </row>
-    <row r="112" spans="1:14">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="8"/>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
@@ -3400,7 +3480,7 @@
       <c r="M112" s="11"/>
       <c r="N112" s="12"/>
     </row>
-    <row r="113" spans="1:14">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="8"/>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
@@ -3422,7 +3502,7 @@
       <c r="M113" s="11"/>
       <c r="N113" s="12"/>
     </row>
-    <row r="114" spans="1:14">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="8"/>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
@@ -3444,7 +3524,7 @@
       <c r="M114" s="11"/>
       <c r="N114" s="12"/>
     </row>
-    <row r="115" spans="1:14">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="8"/>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
@@ -3466,7 +3546,7 @@
       <c r="M115" s="11"/>
       <c r="N115" s="12"/>
     </row>
-    <row r="116" spans="1:14">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="8"/>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
@@ -3488,7 +3568,7 @@
       <c r="M116" s="11"/>
       <c r="N116" s="12"/>
     </row>
-    <row r="117" spans="1:14">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="8"/>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
@@ -3510,7 +3590,7 @@
       <c r="M117" s="11"/>
       <c r="N117" s="12"/>
     </row>
-    <row r="118" spans="1:14">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="8"/>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
@@ -3532,7 +3612,7 @@
       <c r="M118" s="11"/>
       <c r="N118" s="12"/>
     </row>
-    <row r="119" spans="1:14">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="8"/>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
@@ -3554,7 +3634,7 @@
       <c r="M119" s="11"/>
       <c r="N119" s="12"/>
     </row>
-    <row r="120" spans="1:14">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="8"/>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
@@ -3576,7 +3656,7 @@
       <c r="M120" s="11"/>
       <c r="N120" s="12"/>
     </row>
-    <row r="121" spans="1:14">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="8"/>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
@@ -3598,7 +3678,7 @@
       <c r="M121" s="11"/>
       <c r="N121" s="12"/>
     </row>
-    <row r="122" spans="1:14">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="8"/>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
@@ -3620,7 +3700,7 @@
       <c r="M122" s="11"/>
       <c r="N122" s="12"/>
     </row>
-    <row r="123" spans="1:14">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="8"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
@@ -3642,7 +3722,7 @@
       <c r="M123" s="11"/>
       <c r="N123" s="12"/>
     </row>
-    <row r="124" spans="1:14">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="8"/>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
@@ -3664,7 +3744,7 @@
       <c r="M124" s="11"/>
       <c r="N124" s="12"/>
     </row>
-    <row r="125" spans="1:14">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="8"/>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
@@ -3686,7 +3766,7 @@
       <c r="M125" s="11"/>
       <c r="N125" s="12"/>
     </row>
-    <row r="126" spans="1:14">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="8"/>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
@@ -3708,7 +3788,7 @@
       <c r="M126" s="11"/>
       <c r="N126" s="12"/>
     </row>
-    <row r="127" spans="1:14">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="8"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
@@ -3730,7 +3810,7 @@
       <c r="M127" s="11"/>
       <c r="N127" s="12"/>
     </row>
-    <row r="128" spans="1:14">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="8"/>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
@@ -3752,7 +3832,7 @@
       <c r="M128" s="11"/>
       <c r="N128" s="12"/>
     </row>
-    <row r="129" spans="1:14">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="8"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
@@ -3774,7 +3854,7 @@
       <c r="M129" s="11"/>
       <c r="N129" s="12"/>
     </row>
-    <row r="130" spans="1:14">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="8"/>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
@@ -3796,7 +3876,7 @@
       <c r="M130" s="11"/>
       <c r="N130" s="12"/>
     </row>
-    <row r="131" spans="1:14">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="8"/>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
@@ -3818,7 +3898,7 @@
       <c r="M131" s="11"/>
       <c r="N131" s="12"/>
     </row>
-    <row r="132" spans="1:14">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="8"/>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
@@ -3840,7 +3920,7 @@
       <c r="M132" s="11"/>
       <c r="N132" s="12"/>
     </row>
-    <row r="133" spans="1:14">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="8"/>
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
@@ -3862,7 +3942,7 @@
       <c r="M133" s="11"/>
       <c r="N133" s="12"/>
     </row>
-    <row r="134" spans="1:14">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="8"/>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
@@ -3884,7 +3964,7 @@
       <c r="M134" s="11"/>
       <c r="N134" s="12"/>
     </row>
-    <row r="135" spans="1:14">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="8"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
@@ -3906,7 +3986,7 @@
       <c r="M135" s="11"/>
       <c r="N135" s="12"/>
     </row>
-    <row r="136" spans="1:14">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="8"/>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
@@ -3928,7 +4008,7 @@
       <c r="M136" s="11"/>
       <c r="N136" s="12"/>
     </row>
-    <row r="137" spans="1:14">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="8"/>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
@@ -3950,7 +4030,7 @@
       <c r="M137" s="11"/>
       <c r="N137" s="12"/>
     </row>
-    <row r="138" spans="1:14">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="8"/>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
@@ -3972,7 +4052,7 @@
       <c r="M138" s="11"/>
       <c r="N138" s="12"/>
     </row>
-    <row r="139" spans="1:14">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="8"/>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
@@ -3994,7 +4074,7 @@
       <c r="M139" s="11"/>
       <c r="N139" s="12"/>
     </row>
-    <row r="140" spans="1:14">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="8"/>
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
@@ -4016,7 +4096,7 @@
       <c r="M140" s="11"/>
       <c r="N140" s="12"/>
     </row>
-    <row r="141" spans="1:14">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="8"/>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
@@ -4038,7 +4118,7 @@
       <c r="M141" s="11"/>
       <c r="N141" s="12"/>
     </row>
-    <row r="142" spans="1:14">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="8"/>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
@@ -4060,7 +4140,7 @@
       <c r="M142" s="11"/>
       <c r="N142" s="12"/>
     </row>
-    <row r="143" spans="1:14">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="8"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
@@ -4082,7 +4162,7 @@
       <c r="M143" s="11"/>
       <c r="N143" s="12"/>
     </row>
-    <row r="144" spans="1:14">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="8"/>
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
@@ -4104,7 +4184,7 @@
       <c r="M144" s="11"/>
       <c r="N144" s="12"/>
     </row>
-    <row r="145" spans="1:14">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="8"/>
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
@@ -4126,7 +4206,7 @@
       <c r="M145" s="11"/>
       <c r="N145" s="12"/>
     </row>
-    <row r="146" spans="1:14">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="8"/>
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
@@ -4148,7 +4228,7 @@
       <c r="M146" s="11"/>
       <c r="N146" s="12"/>
     </row>
-    <row r="147" spans="1:14">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="8"/>
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
@@ -4170,7 +4250,7 @@
       <c r="M147" s="11"/>
       <c r="N147" s="12"/>
     </row>
-    <row r="148" spans="1:14">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="8"/>
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
@@ -4192,7 +4272,7 @@
       <c r="M148" s="11"/>
       <c r="N148" s="12"/>
     </row>
-    <row r="149" spans="1:14">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="8"/>
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
@@ -4214,7 +4294,7 @@
       <c r="M149" s="11"/>
       <c r="N149" s="12"/>
     </row>
-    <row r="150" spans="1:14">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="8"/>
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
@@ -4236,7 +4316,7 @@
       <c r="M150" s="11"/>
       <c r="N150" s="12"/>
     </row>
-    <row r="151" spans="1:14">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="8"/>
       <c r="B151" s="9"/>
       <c r="C151" s="9"/>
@@ -4258,7 +4338,7 @@
       <c r="M151" s="11"/>
       <c r="N151" s="12"/>
     </row>
-    <row r="152" spans="1:14">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="8"/>
       <c r="B152" s="9"/>
       <c r="C152" s="9"/>
@@ -4280,7 +4360,7 @@
       <c r="M152" s="11"/>
       <c r="N152" s="12"/>
     </row>
-    <row r="153" spans="1:14">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="8"/>
       <c r="B153" s="9"/>
       <c r="C153" s="9"/>
@@ -4302,7 +4382,7 @@
       <c r="M153" s="11"/>
       <c r="N153" s="12"/>
     </row>
-    <row r="154" spans="1:14">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="8"/>
       <c r="B154" s="9"/>
       <c r="C154" s="9"/>
@@ -4324,7 +4404,7 @@
       <c r="M154" s="11"/>
       <c r="N154" s="12"/>
     </row>
-    <row r="155" spans="1:14">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="8"/>
       <c r="B155" s="9"/>
       <c r="C155" s="9"/>
@@ -4346,7 +4426,7 @@
       <c r="M155" s="11"/>
       <c r="N155" s="12"/>
     </row>
-    <row r="156" spans="1:14">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="8"/>
       <c r="B156" s="9"/>
       <c r="C156" s="9"/>
@@ -4368,7 +4448,7 @@
       <c r="M156" s="11"/>
       <c r="N156" s="12"/>
     </row>
-    <row r="157" spans="1:14">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="8"/>
       <c r="B157" s="9"/>
       <c r="C157" s="9"/>
@@ -4390,7 +4470,7 @@
       <c r="M157" s="11"/>
       <c r="N157" s="12"/>
     </row>
-    <row r="158" spans="1:14">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="8"/>
       <c r="B158" s="9"/>
       <c r="C158" s="9"/>
@@ -4412,7 +4492,7 @@
       <c r="M158" s="11"/>
       <c r="N158" s="12"/>
     </row>
-    <row r="159" spans="1:14">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="8"/>
       <c r="B159" s="9"/>
       <c r="C159" s="9"/>
@@ -4434,7 +4514,7 @@
       <c r="M159" s="11"/>
       <c r="N159" s="12"/>
     </row>
-    <row r="160" spans="1:14">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="8"/>
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
@@ -4456,7 +4536,7 @@
       <c r="M160" s="11"/>
       <c r="N160" s="12"/>
     </row>
-    <row r="161" spans="1:14">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="8"/>
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
@@ -4478,7 +4558,7 @@
       <c r="M161" s="11"/>
       <c r="N161" s="12"/>
     </row>
-    <row r="162" spans="1:14">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="8"/>
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
@@ -4500,7 +4580,7 @@
       <c r="M162" s="11"/>
       <c r="N162" s="12"/>
     </row>
-    <row r="163" spans="1:14">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="8"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
@@ -4522,7 +4602,7 @@
       <c r="M163" s="11"/>
       <c r="N163" s="12"/>
     </row>
-    <row r="164" spans="1:14">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="8"/>
       <c r="B164" s="9"/>
       <c r="C164" s="9"/>
@@ -4544,7 +4624,7 @@
       <c r="M164" s="11"/>
       <c r="N164" s="12"/>
     </row>
-    <row r="165" spans="1:14">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="8"/>
       <c r="B165" s="9"/>
       <c r="C165" s="9"/>
@@ -4566,7 +4646,7 @@
       <c r="M165" s="11"/>
       <c r="N165" s="12"/>
     </row>
-    <row r="166" spans="1:14">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="8"/>
       <c r="B166" s="9"/>
       <c r="C166" s="9"/>
@@ -4588,7 +4668,7 @@
       <c r="M166" s="11"/>
       <c r="N166" s="12"/>
     </row>
-    <row r="167" spans="1:14">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="8"/>
       <c r="B167" s="9"/>
       <c r="C167" s="9"/>
@@ -4610,7 +4690,7 @@
       <c r="M167" s="11"/>
       <c r="N167" s="12"/>
     </row>
-    <row r="168" spans="1:14">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="8"/>
       <c r="B168" s="9"/>
       <c r="C168" s="9"/>
@@ -4632,7 +4712,7 @@
       <c r="M168" s="11"/>
       <c r="N168" s="12"/>
     </row>
-    <row r="169" spans="1:14">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="8"/>
       <c r="B169" s="9"/>
       <c r="C169" s="9"/>
@@ -4654,7 +4734,7 @@
       <c r="M169" s="11"/>
       <c r="N169" s="12"/>
     </row>
-    <row r="170" spans="1:14">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="8"/>
       <c r="B170" s="9"/>
       <c r="C170" s="9"/>
@@ -4676,7 +4756,7 @@
       <c r="M170" s="11"/>
       <c r="N170" s="12"/>
     </row>
-    <row r="171" spans="1:14">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="8"/>
       <c r="B171" s="9"/>
       <c r="C171" s="9"/>
@@ -4698,7 +4778,7 @@
       <c r="M171" s="11"/>
       <c r="N171" s="12"/>
     </row>
-    <row r="172" spans="1:14">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="8"/>
       <c r="B172" s="9"/>
       <c r="C172" s="9"/>
@@ -4720,7 +4800,7 @@
       <c r="M172" s="11"/>
       <c r="N172" s="12"/>
     </row>
-    <row r="173" spans="1:14">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="8"/>
       <c r="B173" s="9"/>
       <c r="C173" s="9"/>
@@ -4742,7 +4822,7 @@
       <c r="M173" s="11"/>
       <c r="N173" s="12"/>
     </row>
-    <row r="174" spans="1:14">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="8"/>
       <c r="B174" s="9"/>
       <c r="C174" s="9"/>
@@ -4764,7 +4844,7 @@
       <c r="M174" s="11"/>
       <c r="N174" s="12"/>
     </row>
-    <row r="175" spans="1:14">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="8"/>
       <c r="B175" s="9"/>
       <c r="C175" s="9"/>
@@ -4786,7 +4866,7 @@
       <c r="M175" s="11"/>
       <c r="N175" s="12"/>
     </row>
-    <row r="176" spans="1:14">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="8"/>
       <c r="B176" s="9"/>
       <c r="C176" s="9"/>
@@ -4808,7 +4888,7 @@
       <c r="M176" s="11"/>
       <c r="N176" s="12"/>
     </row>
-    <row r="177" spans="1:14">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="8"/>
       <c r="B177" s="9"/>
       <c r="C177" s="9"/>
@@ -4830,7 +4910,7 @@
       <c r="M177" s="11"/>
       <c r="N177" s="12"/>
     </row>
-    <row r="178" spans="1:14">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="8"/>
       <c r="B178" s="9"/>
       <c r="C178" s="9"/>
@@ -4852,7 +4932,7 @@
       <c r="M178" s="11"/>
       <c r="N178" s="12"/>
     </row>
-    <row r="179" spans="1:14">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="8"/>
       <c r="B179" s="9"/>
       <c r="C179" s="9"/>
@@ -4874,7 +4954,7 @@
       <c r="M179" s="11"/>
       <c r="N179" s="12"/>
     </row>
-    <row r="180" spans="1:14">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="8"/>
       <c r="B180" s="9"/>
       <c r="C180" s="9"/>
@@ -4896,7 +4976,7 @@
       <c r="M180" s="11"/>
       <c r="N180" s="12"/>
     </row>
-    <row r="181" spans="1:14">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="8"/>
       <c r="B181" s="9"/>
       <c r="C181" s="9"/>
@@ -4918,7 +4998,7 @@
       <c r="M181" s="11"/>
       <c r="N181" s="12"/>
     </row>
-    <row r="182" spans="1:14">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="8"/>
       <c r="B182" s="9"/>
       <c r="C182" s="9"/>
@@ -4940,7 +5020,7 @@
       <c r="M182" s="11"/>
       <c r="N182" s="12"/>
     </row>
-    <row r="183" spans="1:14">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="8"/>
       <c r="B183" s="9"/>
       <c r="C183" s="9"/>
@@ -4962,7 +5042,7 @@
       <c r="M183" s="11"/>
       <c r="N183" s="12"/>
     </row>
-    <row r="184" spans="1:14">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="8"/>
       <c r="B184" s="9"/>
       <c r="C184" s="9"/>
@@ -4984,7 +5064,7 @@
       <c r="M184" s="11"/>
       <c r="N184" s="12"/>
     </row>
-    <row r="185" spans="1:14">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="8"/>
       <c r="B185" s="9"/>
       <c r="C185" s="9"/>
@@ -5006,7 +5086,7 @@
       <c r="M185" s="11"/>
       <c r="N185" s="12"/>
     </row>
-    <row r="186" spans="1:14">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="8"/>
       <c r="B186" s="9"/>
       <c r="C186" s="9"/>
@@ -5028,7 +5108,7 @@
       <c r="M186" s="11"/>
       <c r="N186" s="12"/>
     </row>
-    <row r="187" spans="1:14">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="8"/>
       <c r="B187" s="9"/>
       <c r="C187" s="9"/>
@@ -5050,7 +5130,7 @@
       <c r="M187" s="11"/>
       <c r="N187" s="12"/>
     </row>
-    <row r="188" spans="1:14">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="8"/>
       <c r="B188" s="9"/>
       <c r="C188" s="9"/>
@@ -5072,7 +5152,7 @@
       <c r="M188" s="11"/>
       <c r="N188" s="12"/>
     </row>
-    <row r="189" spans="1:14">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="8"/>
       <c r="B189" s="9"/>
       <c r="C189" s="9"/>
@@ -5094,7 +5174,7 @@
       <c r="M189" s="11"/>
       <c r="N189" s="12"/>
     </row>
-    <row r="190" spans="1:14">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="8"/>
       <c r="B190" s="9"/>
       <c r="C190" s="9"/>
@@ -5116,7 +5196,7 @@
       <c r="M190" s="11"/>
       <c r="N190" s="12"/>
     </row>
-    <row r="191" spans="1:14">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="8"/>
       <c r="B191" s="9"/>
       <c r="C191" s="9"/>
@@ -5138,7 +5218,7 @@
       <c r="M191" s="11"/>
       <c r="N191" s="12"/>
     </row>
-    <row r="192" spans="1:14">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="8"/>
       <c r="B192" s="9"/>
       <c r="C192" s="9"/>
@@ -5160,7 +5240,7 @@
       <c r="M192" s="11"/>
       <c r="N192" s="12"/>
     </row>
-    <row r="193" spans="1:14">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="8"/>
       <c r="B193" s="9"/>
       <c r="C193" s="9"/>
@@ -5182,7 +5262,7 @@
       <c r="M193" s="11"/>
       <c r="N193" s="12"/>
     </row>
-    <row r="194" spans="1:14">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="8"/>
       <c r="B194" s="9"/>
       <c r="C194" s="9"/>
@@ -5204,7 +5284,7 @@
       <c r="M194" s="11"/>
       <c r="N194" s="12"/>
     </row>
-    <row r="195" spans="1:14">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="8"/>
       <c r="B195" s="9"/>
       <c r="C195" s="9"/>
@@ -5226,7 +5306,7 @@
       <c r="M195" s="11"/>
       <c r="N195" s="12"/>
     </row>
-    <row r="196" spans="1:14">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="8"/>
       <c r="B196" s="9"/>
       <c r="C196" s="9"/>
@@ -5248,7 +5328,7 @@
       <c r="M196" s="11"/>
       <c r="N196" s="12"/>
     </row>
-    <row r="197" spans="1:14">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="8"/>
       <c r="B197" s="9"/>
       <c r="C197" s="9"/>
@@ -5270,7 +5350,7 @@
       <c r="M197" s="11"/>
       <c r="N197" s="12"/>
     </row>
-    <row r="198" spans="1:14">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="8"/>
       <c r="B198" s="9"/>
       <c r="C198" s="9"/>
@@ -5292,7 +5372,7 @@
       <c r="M198" s="11"/>
       <c r="N198" s="12"/>
     </row>
-    <row r="199" spans="1:14">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="8"/>
       <c r="B199" s="9"/>
       <c r="C199" s="9"/>
@@ -5314,7 +5394,7 @@
       <c r="M199" s="11"/>
       <c r="N199" s="12"/>
     </row>
-    <row r="200" spans="1:14">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="8"/>
       <c r="B200" s="9"/>
       <c r="C200" s="9"/>
@@ -5336,7 +5416,7 @@
       <c r="M200" s="11"/>
       <c r="N200" s="12"/>
     </row>
-    <row r="201" spans="1:14">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="8"/>
       <c r="B201" s="9"/>
       <c r="C201" s="9"/>
@@ -5358,7 +5438,7 @@
       <c r="M201" s="11"/>
       <c r="N201" s="12"/>
     </row>
-    <row r="202" spans="1:14">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="8"/>
       <c r="B202" s="9"/>
       <c r="C202" s="9"/>
@@ -5380,7 +5460,7 @@
       <c r="M202" s="11"/>
       <c r="N202" s="12"/>
     </row>
-    <row r="203" spans="1:14">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="8"/>
       <c r="B203" s="9"/>
       <c r="C203" s="9"/>
@@ -5402,7 +5482,7 @@
       <c r="M203" s="11"/>
       <c r="N203" s="12"/>
     </row>
-    <row r="204" spans="1:14">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="8"/>
       <c r="B204" s="9"/>
       <c r="C204" s="9"/>
@@ -5424,7 +5504,7 @@
       <c r="M204" s="11"/>
       <c r="N204" s="12"/>
     </row>
-    <row r="205" spans="1:14">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="8"/>
       <c r="B205" s="9"/>
       <c r="C205" s="9"/>
@@ -5446,7 +5526,7 @@
       <c r="M205" s="11"/>
       <c r="N205" s="12"/>
     </row>
-    <row r="206" spans="1:14">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="8"/>
       <c r="B206" s="9"/>
       <c r="C206" s="9"/>
@@ -5468,7 +5548,7 @@
       <c r="M206" s="11"/>
       <c r="N206" s="12"/>
     </row>
-    <row r="207" spans="1:14">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="8"/>
       <c r="B207" s="9"/>
       <c r="C207" s="9"/>
@@ -5490,7 +5570,7 @@
       <c r="M207" s="11"/>
       <c r="N207" s="12"/>
     </row>
-    <row r="208" spans="1:14">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="8"/>
       <c r="B208" s="9"/>
       <c r="C208" s="9"/>
@@ -5512,7 +5592,7 @@
       <c r="M208" s="11"/>
       <c r="N208" s="12"/>
     </row>
-    <row r="209" spans="1:14">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="8"/>
       <c r="B209" s="9"/>
       <c r="C209" s="9"/>
@@ -5534,7 +5614,7 @@
       <c r="M209" s="11"/>
       <c r="N209" s="12"/>
     </row>
-    <row r="210" spans="1:14">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" s="8"/>
       <c r="B210" s="9"/>
       <c r="C210" s="9"/>
@@ -5556,7 +5636,7 @@
       <c r="M210" s="11"/>
       <c r="N210" s="12"/>
     </row>
-    <row r="211" spans="1:14">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" s="8"/>
       <c r="B211" s="9"/>
       <c r="C211" s="9"/>
@@ -5578,7 +5658,7 @@
       <c r="M211" s="11"/>
       <c r="N211" s="12"/>
     </row>
-    <row r="212" spans="1:14">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="8"/>
       <c r="B212" s="9"/>
       <c r="C212" s="9"/>
@@ -5600,7 +5680,7 @@
       <c r="M212" s="11"/>
       <c r="N212" s="12"/>
     </row>
-    <row r="213" spans="1:14">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="8"/>
       <c r="B213" s="9"/>
       <c r="C213" s="9"/>
@@ -5622,7 +5702,7 @@
       <c r="M213" s="11"/>
       <c r="N213" s="12"/>
     </row>
-    <row r="214" spans="1:14">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="8"/>
       <c r="B214" s="9"/>
       <c r="C214" s="9"/>
@@ -5644,7 +5724,7 @@
       <c r="M214" s="11"/>
       <c r="N214" s="12"/>
     </row>
-    <row r="215" spans="1:14">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="8"/>
       <c r="B215" s="9"/>
       <c r="C215" s="9"/>
@@ -5666,7 +5746,7 @@
       <c r="M215" s="11"/>
       <c r="N215" s="12"/>
     </row>
-    <row r="216" spans="1:14">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="8"/>
       <c r="B216" s="9"/>
       <c r="C216" s="9"/>
@@ -5688,7 +5768,7 @@
       <c r="M216" s="11"/>
       <c r="N216" s="12"/>
     </row>
-    <row r="217" spans="1:14">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="8"/>
       <c r="B217" s="9"/>
       <c r="C217" s="9"/>
@@ -5710,7 +5790,7 @@
       <c r="M217" s="11"/>
       <c r="N217" s="12"/>
     </row>
-    <row r="218" spans="1:14">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="8"/>
       <c r="B218" s="9"/>
       <c r="C218" s="9"/>
@@ -5732,7 +5812,7 @@
       <c r="M218" s="11"/>
       <c r="N218" s="12"/>
     </row>
-    <row r="219" spans="1:14">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="8"/>
       <c r="B219" s="9"/>
       <c r="C219" s="9"/>
@@ -5754,7 +5834,7 @@
       <c r="M219" s="11"/>
       <c r="N219" s="12"/>
     </row>
-    <row r="220" spans="1:14">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="8"/>
       <c r="B220" s="9"/>
       <c r="C220" s="9"/>
@@ -5776,7 +5856,7 @@
       <c r="M220" s="11"/>
       <c r="N220" s="12"/>
     </row>
-    <row r="221" spans="1:14">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="8"/>
       <c r="B221" s="9"/>
       <c r="C221" s="9"/>
@@ -5798,7 +5878,7 @@
       <c r="M221" s="11"/>
       <c r="N221" s="12"/>
     </row>
-    <row r="222" spans="1:14">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="8"/>
       <c r="B222" s="9"/>
       <c r="C222" s="9"/>
@@ -5820,7 +5900,7 @@
       <c r="M222" s="11"/>
       <c r="N222" s="12"/>
     </row>
-    <row r="223" spans="1:14">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" s="8"/>
       <c r="B223" s="9"/>
       <c r="C223" s="9"/>
@@ -5842,7 +5922,7 @@
       <c r="M223" s="11"/>
       <c r="N223" s="12"/>
     </row>
-    <row r="224" spans="1:14">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" s="8"/>
       <c r="B224" s="9"/>
       <c r="C224" s="9"/>
@@ -5864,7 +5944,7 @@
       <c r="M224" s="11"/>
       <c r="N224" s="12"/>
     </row>
-    <row r="225" spans="1:14">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" s="8"/>
       <c r="B225" s="9"/>
       <c r="C225" s="9"/>
@@ -5886,7 +5966,7 @@
       <c r="M225" s="11"/>
       <c r="N225" s="12"/>
     </row>
-    <row r="226" spans="1:14">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" s="8"/>
       <c r="B226" s="9"/>
       <c r="C226" s="9"/>
@@ -5908,7 +5988,7 @@
       <c r="M226" s="11"/>
       <c r="N226" s="12"/>
     </row>
-    <row r="227" spans="1:14">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" s="8"/>
       <c r="B227" s="9"/>
       <c r="C227" s="9"/>
@@ -5930,7 +6010,7 @@
       <c r="M227" s="11"/>
       <c r="N227" s="12"/>
     </row>
-    <row r="228" spans="1:14">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" s="8"/>
       <c r="B228" s="9"/>
       <c r="C228" s="9"/>
@@ -5952,7 +6032,7 @@
       <c r="M228" s="11"/>
       <c r="N228" s="12"/>
     </row>
-    <row r="229" spans="1:14">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" s="8"/>
       <c r="B229" s="9"/>
       <c r="C229" s="9"/>
@@ -5974,7 +6054,7 @@
       <c r="M229" s="11"/>
       <c r="N229" s="12"/>
     </row>
-    <row r="230" spans="1:14">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" s="8"/>
       <c r="B230" s="9"/>
       <c r="C230" s="9"/>
@@ -5996,7 +6076,7 @@
       <c r="M230" s="11"/>
       <c r="N230" s="12"/>
     </row>
-    <row r="231" spans="1:14">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" s="8"/>
       <c r="B231" s="9"/>
       <c r="C231" s="9"/>
@@ -6018,7 +6098,7 @@
       <c r="M231" s="11"/>
       <c r="N231" s="12"/>
     </row>
-    <row r="232" spans="1:14">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" s="8"/>
       <c r="B232" s="9"/>
       <c r="C232" s="9"/>
@@ -6040,7 +6120,7 @@
       <c r="M232" s="11"/>
       <c r="N232" s="12"/>
     </row>
-    <row r="233" spans="1:14">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" s="8"/>
       <c r="B233" s="9"/>
       <c r="C233" s="9"/>
@@ -6062,7 +6142,7 @@
       <c r="M233" s="11"/>
       <c r="N233" s="12"/>
     </row>
-    <row r="234" spans="1:14">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" s="8"/>
       <c r="B234" s="9"/>
       <c r="C234" s="9"/>
@@ -6084,7 +6164,7 @@
       <c r="M234" s="11"/>
       <c r="N234" s="12"/>
     </row>
-    <row r="235" spans="1:14">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" s="8"/>
       <c r="B235" s="9"/>
       <c r="C235" s="9"/>
@@ -6106,7 +6186,7 @@
       <c r="M235" s="11"/>
       <c r="N235" s="12"/>
     </row>
-    <row r="236" spans="1:14">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" s="8"/>
       <c r="B236" s="9"/>
       <c r="C236" s="9"/>
@@ -6128,7 +6208,7 @@
       <c r="M236" s="11"/>
       <c r="N236" s="12"/>
     </row>
-    <row r="237" spans="1:14">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" s="8"/>
       <c r="B237" s="9"/>
       <c r="C237" s="9"/>
@@ -6150,7 +6230,7 @@
       <c r="M237" s="11"/>
       <c r="N237" s="12"/>
     </row>
-    <row r="238" spans="1:14">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" s="8"/>
       <c r="B238" s="9"/>
       <c r="C238" s="9"/>
@@ -6172,7 +6252,7 @@
       <c r="M238" s="11"/>
       <c r="N238" s="12"/>
     </row>
-    <row r="239" spans="1:14">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" s="8"/>
       <c r="B239" s="9"/>
       <c r="C239" s="9"/>
@@ -6194,7 +6274,7 @@
       <c r="M239" s="11"/>
       <c r="N239" s="12"/>
     </row>
-    <row r="240" spans="1:14">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240" s="8"/>
       <c r="B240" s="9"/>
       <c r="C240" s="9"/>
@@ -6216,7 +6296,7 @@
       <c r="M240" s="11"/>
       <c r="N240" s="12"/>
     </row>
-    <row r="241" spans="1:14">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241" s="8"/>
       <c r="B241" s="9"/>
       <c r="C241" s="9"/>
@@ -6238,7 +6318,7 @@
       <c r="M241" s="11"/>
       <c r="N241" s="12"/>
     </row>
-    <row r="242" spans="1:14">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242" s="8"/>
       <c r="B242" s="9"/>
       <c r="C242" s="9"/>
@@ -6260,7 +6340,7 @@
       <c r="M242" s="11"/>
       <c r="N242" s="12"/>
     </row>
-    <row r="243" spans="1:14">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243" s="8"/>
       <c r="B243" s="9"/>
       <c r="C243" s="9"/>
@@ -6282,7 +6362,7 @@
       <c r="M243" s="11"/>
       <c r="N243" s="12"/>
     </row>
-    <row r="244" spans="1:14">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244" s="8"/>
       <c r="B244" s="9"/>
       <c r="C244" s="9"/>
@@ -6304,7 +6384,7 @@
       <c r="M244" s="11"/>
       <c r="N244" s="12"/>
     </row>
-    <row r="245" spans="1:14">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245" s="8"/>
       <c r="B245" s="9"/>
       <c r="C245" s="9"/>
@@ -6326,7 +6406,7 @@
       <c r="M245" s="11"/>
       <c r="N245" s="12"/>
     </row>
-    <row r="246" spans="1:14">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246" s="8"/>
       <c r="B246" s="9"/>
       <c r="C246" s="9"/>
@@ -6348,7 +6428,7 @@
       <c r="M246" s="11"/>
       <c r="N246" s="12"/>
     </row>
-    <row r="247" spans="1:14">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247" s="8"/>
       <c r="B247" s="9"/>
       <c r="C247" s="9"/>
@@ -6370,7 +6450,7 @@
       <c r="M247" s="11"/>
       <c r="N247" s="12"/>
     </row>
-    <row r="248" spans="1:14">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248" s="8"/>
       <c r="B248" s="9"/>
       <c r="C248" s="9"/>
@@ -6392,7 +6472,7 @@
       <c r="M248" s="11"/>
       <c r="N248" s="12"/>
     </row>
-    <row r="249" spans="1:14">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249" s="8"/>
       <c r="B249" s="9"/>
       <c r="C249" s="9"/>
@@ -6414,7 +6494,7 @@
       <c r="M249" s="11"/>
       <c r="N249" s="12"/>
     </row>
-    <row r="250" spans="1:14">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250" s="8"/>
       <c r="B250" s="9"/>
       <c r="C250" s="9"/>
@@ -6436,7 +6516,7 @@
       <c r="M250" s="11"/>
       <c r="N250" s="12"/>
     </row>
-    <row r="251" spans="1:14">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251" s="8"/>
       <c r="B251" s="9"/>
       <c r="C251" s="9"/>
@@ -6458,7 +6538,7 @@
       <c r="M251" s="11"/>
       <c r="N251" s="12"/>
     </row>
-    <row r="252" spans="1:14">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252" s="8"/>
       <c r="B252" s="9"/>
       <c r="C252" s="9"/>
@@ -6480,7 +6560,7 @@
       <c r="M252" s="11"/>
       <c r="N252" s="12"/>
     </row>
-    <row r="253" spans="1:14">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253" s="8"/>
       <c r="B253" s="9"/>
       <c r="C253" s="9"/>
@@ -6502,7 +6582,7 @@
       <c r="M253" s="11"/>
       <c r="N253" s="12"/>
     </row>
-    <row r="254" spans="1:14">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254" s="8"/>
       <c r="B254" s="9"/>
       <c r="C254" s="9"/>
@@ -6524,7 +6604,7 @@
       <c r="M254" s="11"/>
       <c r="N254" s="12"/>
     </row>
-    <row r="255" spans="1:14">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255" s="8"/>
       <c r="B255" s="9"/>
       <c r="C255" s="9"/>
@@ -6546,7 +6626,7 @@
       <c r="M255" s="11"/>
       <c r="N255" s="12"/>
     </row>
-    <row r="256" spans="1:14">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256" s="8"/>
       <c r="B256" s="9"/>
       <c r="C256" s="9"/>
@@ -6568,7 +6648,7 @@
       <c r="M256" s="11"/>
       <c r="N256" s="12"/>
     </row>
-    <row r="257" spans="1:14">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" s="8"/>
       <c r="B257" s="9"/>
       <c r="C257" s="9"/>
@@ -6590,7 +6670,7 @@
       <c r="M257" s="11"/>
       <c r="N257" s="12"/>
     </row>
-    <row r="258" spans="1:14">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" s="8"/>
       <c r="B258" s="9"/>
       <c r="C258" s="9"/>
@@ -6612,7 +6692,7 @@
       <c r="M258" s="11"/>
       <c r="N258" s="12"/>
     </row>
-    <row r="259" spans="1:14">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" s="8"/>
       <c r="B259" s="9"/>
       <c r="C259" s="9"/>
@@ -6634,7 +6714,7 @@
       <c r="M259" s="11"/>
       <c r="N259" s="12"/>
     </row>
-    <row r="260" spans="1:14">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" s="8"/>
       <c r="B260" s="9"/>
       <c r="C260" s="9"/>
@@ -6656,7 +6736,7 @@
       <c r="M260" s="11"/>
       <c r="N260" s="12"/>
     </row>
-    <row r="261" spans="1:14">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" s="8"/>
       <c r="B261" s="9"/>
       <c r="C261" s="9"/>
@@ -6678,7 +6758,7 @@
       <c r="M261" s="11"/>
       <c r="N261" s="12"/>
     </row>
-    <row r="262" spans="1:14">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" s="8"/>
       <c r="B262" s="9"/>
       <c r="C262" s="9"/>
@@ -6700,7 +6780,7 @@
       <c r="M262" s="11"/>
       <c r="N262" s="12"/>
     </row>
-    <row r="263" spans="1:14">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" s="8"/>
       <c r="B263" s="9"/>
       <c r="C263" s="9"/>
@@ -6722,7 +6802,7 @@
       <c r="M263" s="11"/>
       <c r="N263" s="12"/>
     </row>
-    <row r="264" spans="1:14">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" s="8"/>
       <c r="B264" s="9"/>
       <c r="C264" s="9"/>
@@ -6744,7 +6824,7 @@
       <c r="M264" s="11"/>
       <c r="N264" s="12"/>
     </row>
-    <row r="265" spans="1:14">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" s="8"/>
       <c r="B265" s="9"/>
       <c r="C265" s="9"/>
@@ -6766,7 +6846,7 @@
       <c r="M265" s="11"/>
       <c r="N265" s="12"/>
     </row>
-    <row r="266" spans="1:14">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266" s="8"/>
       <c r="B266" s="9"/>
       <c r="C266" s="9"/>
@@ -6788,7 +6868,7 @@
       <c r="M266" s="11"/>
       <c r="N266" s="12"/>
     </row>
-    <row r="267" spans="1:14">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" s="8"/>
       <c r="B267" s="9"/>
       <c r="C267" s="9"/>
@@ -6810,7 +6890,7 @@
       <c r="M267" s="11"/>
       <c r="N267" s="12"/>
     </row>
-    <row r="268" spans="1:14">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" s="8"/>
       <c r="B268" s="9"/>
       <c r="C268" s="9"/>
@@ -6832,7 +6912,7 @@
       <c r="M268" s="11"/>
       <c r="N268" s="12"/>
     </row>
-    <row r="269" spans="1:14">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" s="8"/>
       <c r="B269" s="9"/>
       <c r="C269" s="9"/>
@@ -6854,7 +6934,7 @@
       <c r="M269" s="11"/>
       <c r="N269" s="12"/>
     </row>
-    <row r="270" spans="1:14">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" s="8"/>
       <c r="B270" s="9"/>
       <c r="C270" s="9"/>
@@ -6876,7 +6956,7 @@
       <c r="M270" s="11"/>
       <c r="N270" s="12"/>
     </row>
-    <row r="271" spans="1:14">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" s="8"/>
       <c r="B271" s="9"/>
       <c r="C271" s="9"/>
@@ -6898,7 +6978,7 @@
       <c r="M271" s="11"/>
       <c r="N271" s="12"/>
     </row>
-    <row r="272" spans="1:14">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" s="8"/>
       <c r="B272" s="9"/>
       <c r="C272" s="9"/>
@@ -6920,7 +7000,7 @@
       <c r="M272" s="11"/>
       <c r="N272" s="12"/>
     </row>
-    <row r="273" spans="1:14">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" s="8"/>
       <c r="B273" s="9"/>
       <c r="C273" s="9"/>
@@ -6942,7 +7022,7 @@
       <c r="M273" s="11"/>
       <c r="N273" s="12"/>
     </row>
-    <row r="274" spans="1:14">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" s="8"/>
       <c r="B274" s="9"/>
       <c r="C274" s="9"/>
@@ -6964,7 +7044,7 @@
       <c r="M274" s="11"/>
       <c r="N274" s="12"/>
     </row>
-    <row r="275" spans="1:14">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" s="8"/>
       <c r="B275" s="9"/>
       <c r="C275" s="9"/>
@@ -6986,7 +7066,7 @@
       <c r="M275" s="11"/>
       <c r="N275" s="12"/>
     </row>
-    <row r="276" spans="1:14">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" s="8"/>
       <c r="B276" s="9"/>
       <c r="C276" s="9"/>
@@ -7008,7 +7088,7 @@
       <c r="M276" s="11"/>
       <c r="N276" s="12"/>
     </row>
-    <row r="277" spans="1:14">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" s="8"/>
       <c r="B277" s="9"/>
       <c r="C277" s="9"/>
@@ -7030,7 +7110,7 @@
       <c r="M277" s="11"/>
       <c r="N277" s="12"/>
     </row>
-    <row r="278" spans="1:14">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" s="8"/>
       <c r="B278" s="9"/>
       <c r="C278" s="9"/>
@@ -7052,7 +7132,7 @@
       <c r="M278" s="11"/>
       <c r="N278" s="12"/>
     </row>
-    <row r="279" spans="1:14">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" s="8"/>
       <c r="B279" s="9"/>
       <c r="C279" s="9"/>
@@ -7074,7 +7154,7 @@
       <c r="M279" s="11"/>
       <c r="N279" s="12"/>
     </row>
-    <row r="280" spans="1:14">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" s="8"/>
       <c r="B280" s="9"/>
       <c r="C280" s="9"/>
@@ -7096,7 +7176,7 @@
       <c r="M280" s="11"/>
       <c r="N280" s="12"/>
     </row>
-    <row r="281" spans="1:14">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" s="8"/>
       <c r="B281" s="9"/>
       <c r="C281" s="9"/>
@@ -7118,7 +7198,7 @@
       <c r="M281" s="11"/>
       <c r="N281" s="12"/>
     </row>
-    <row r="282" spans="1:14">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" s="8"/>
       <c r="B282" s="9"/>
       <c r="C282" s="9"/>
@@ -7140,7 +7220,7 @@
       <c r="M282" s="11"/>
       <c r="N282" s="12"/>
     </row>
-    <row r="283" spans="1:14">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" s="8"/>
       <c r="B283" s="9"/>
       <c r="C283" s="9"/>
@@ -7162,7 +7242,7 @@
       <c r="M283" s="11"/>
       <c r="N283" s="12"/>
     </row>
-    <row r="284" spans="1:14">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" s="8"/>
       <c r="B284" s="9"/>
       <c r="C284" s="9"/>
@@ -7184,7 +7264,7 @@
       <c r="M284" s="11"/>
       <c r="N284" s="12"/>
     </row>
-    <row r="285" spans="1:14">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" s="8"/>
       <c r="B285" s="9"/>
       <c r="C285" s="9"/>
@@ -7206,7 +7286,7 @@
       <c r="M285" s="11"/>
       <c r="N285" s="12"/>
     </row>
-    <row r="286" spans="1:14">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" s="8"/>
       <c r="B286" s="9"/>
       <c r="C286" s="9"/>
@@ -7228,7 +7308,7 @@
       <c r="M286" s="11"/>
       <c r="N286" s="12"/>
     </row>
-    <row r="287" spans="1:14">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" s="8"/>
       <c r="B287" s="9"/>
       <c r="C287" s="9"/>
@@ -7250,7 +7330,7 @@
       <c r="M287" s="11"/>
       <c r="N287" s="12"/>
     </row>
-    <row r="288" spans="1:14">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" s="8"/>
       <c r="B288" s="9"/>
       <c r="C288" s="9"/>
@@ -7272,7 +7352,7 @@
       <c r="M288" s="11"/>
       <c r="N288" s="12"/>
     </row>
-    <row r="289" spans="1:14">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" s="8"/>
       <c r="B289" s="9"/>
       <c r="C289" s="9"/>
@@ -7294,7 +7374,7 @@
       <c r="M289" s="11"/>
       <c r="N289" s="12"/>
     </row>
-    <row r="290" spans="1:14">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" s="8"/>
       <c r="B290" s="9"/>
       <c r="C290" s="9"/>
@@ -7316,7 +7396,7 @@
       <c r="M290" s="11"/>
       <c r="N290" s="12"/>
     </row>
-    <row r="291" spans="1:14">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" s="8"/>
       <c r="B291" s="9"/>
       <c r="C291" s="9"/>
@@ -7338,7 +7418,7 @@
       <c r="M291" s="11"/>
       <c r="N291" s="12"/>
     </row>
-    <row r="292" spans="1:14">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" s="8"/>
       <c r="B292" s="9"/>
       <c r="C292" s="9"/>
@@ -7360,7 +7440,7 @@
       <c r="M292" s="11"/>
       <c r="N292" s="12"/>
     </row>
-    <row r="293" spans="1:14">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" s="8"/>
       <c r="B293" s="9"/>
       <c r="C293" s="9"/>
@@ -7382,7 +7462,7 @@
       <c r="M293" s="11"/>
       <c r="N293" s="12"/>
     </row>
-    <row r="294" spans="1:14">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" s="8"/>
       <c r="B294" s="9"/>
       <c r="C294" s="9"/>
@@ -7404,7 +7484,7 @@
       <c r="M294" s="11"/>
       <c r="N294" s="12"/>
     </row>
-    <row r="295" spans="1:14">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" s="8"/>
       <c r="B295" s="9"/>
       <c r="C295" s="9"/>
@@ -7426,7 +7506,7 @@
       <c r="M295" s="11"/>
       <c r="N295" s="12"/>
     </row>
-    <row r="296" spans="1:14">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" s="8"/>
       <c r="B296" s="9"/>
       <c r="C296" s="9"/>
@@ -7448,7 +7528,7 @@
       <c r="M296" s="11"/>
       <c r="N296" s="12"/>
     </row>
-    <row r="297" spans="1:14">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" s="8"/>
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
@@ -7470,7 +7550,7 @@
       <c r="M297" s="11"/>
       <c r="N297" s="12"/>
     </row>
-    <row r="298" spans="1:14">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" s="8"/>
       <c r="B298" s="9"/>
       <c r="C298" s="9"/>
@@ -7492,7 +7572,7 @@
       <c r="M298" s="11"/>
       <c r="N298" s="12"/>
     </row>
-    <row r="299" spans="1:14">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" s="8"/>
       <c r="B299" s="9"/>
       <c r="C299" s="9"/>
@@ -7514,7 +7594,7 @@
       <c r="M299" s="11"/>
       <c r="N299" s="12"/>
     </row>
-    <row r="300" spans="1:14">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="8"/>
       <c r="B300" s="9"/>
       <c r="C300" s="9"/>
@@ -7536,7 +7616,7 @@
       <c r="M300" s="11"/>
       <c r="N300" s="12"/>
     </row>
-    <row r="301" spans="1:14">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" s="8"/>
       <c r="B301" s="9"/>
       <c r="C301" s="9"/>
@@ -7558,7 +7638,7 @@
       <c r="M301" s="11"/>
       <c r="N301" s="12"/>
     </row>
-    <row r="302" spans="1:14">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" s="8"/>
       <c r="B302" s="9"/>
       <c r="C302" s="9"/>
@@ -7580,7 +7660,7 @@
       <c r="M302" s="11"/>
       <c r="N302" s="12"/>
     </row>
-    <row r="303" spans="1:14">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" s="8"/>
       <c r="B303" s="9"/>
       <c r="C303" s="9"/>
@@ -7602,7 +7682,7 @@
       <c r="M303" s="11"/>
       <c r="N303" s="12"/>
     </row>
-    <row r="304" spans="1:14">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" s="8"/>
       <c r="B304" s="9"/>
       <c r="C304" s="9"/>
@@ -7624,7 +7704,7 @@
       <c r="M304" s="11"/>
       <c r="N304" s="12"/>
     </row>
-    <row r="305" spans="1:14">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="8"/>
       <c r="B305" s="9"/>
       <c r="C305" s="9"/>
@@ -7646,7 +7726,7 @@
       <c r="M305" s="11"/>
       <c r="N305" s="12"/>
     </row>
-    <row r="306" spans="1:14">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" s="8"/>
       <c r="B306" s="9"/>
       <c r="C306" s="9"/>
@@ -7668,7 +7748,7 @@
       <c r="M306" s="11"/>
       <c r="N306" s="12"/>
     </row>
-    <row r="307" spans="1:14">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" s="8"/>
       <c r="B307" s="9"/>
       <c r="C307" s="9"/>
@@ -7690,7 +7770,7 @@
       <c r="M307" s="11"/>
       <c r="N307" s="12"/>
     </row>
-    <row r="308" spans="1:14">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" s="8"/>
       <c r="B308" s="9"/>
       <c r="C308" s="9"/>
@@ -7712,7 +7792,7 @@
       <c r="M308" s="11"/>
       <c r="N308" s="12"/>
     </row>
-    <row r="309" spans="1:14">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" s="8"/>
       <c r="B309" s="9"/>
       <c r="C309" s="9"/>
@@ -7734,7 +7814,7 @@
       <c r="M309" s="11"/>
       <c r="N309" s="12"/>
     </row>
-    <row r="310" spans="1:14">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" s="8"/>
       <c r="B310" s="9"/>
       <c r="C310" s="9"/>
@@ -7756,7 +7836,7 @@
       <c r="M310" s="11"/>
       <c r="N310" s="12"/>
     </row>
-    <row r="311" spans="1:14">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" s="8"/>
       <c r="B311" s="9"/>
       <c r="C311" s="9"/>
@@ -7778,7 +7858,7 @@
       <c r="M311" s="11"/>
       <c r="N311" s="12"/>
     </row>
-    <row r="312" spans="1:14">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" s="8"/>
       <c r="B312" s="9"/>
       <c r="C312" s="9"/>
@@ -7800,7 +7880,7 @@
       <c r="M312" s="11"/>
       <c r="N312" s="12"/>
     </row>
-    <row r="313" spans="1:14">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" s="8"/>
       <c r="B313" s="9"/>
       <c r="C313" s="9"/>
@@ -7822,7 +7902,7 @@
       <c r="M313" s="11"/>
       <c r="N313" s="12"/>
     </row>
-    <row r="314" spans="1:14">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" s="8"/>
       <c r="B314" s="9"/>
       <c r="C314" s="9"/>
@@ -7844,7 +7924,7 @@
       <c r="M314" s="11"/>
       <c r="N314" s="12"/>
     </row>
-    <row r="315" spans="1:14">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" s="8"/>
       <c r="B315" s="9"/>
       <c r="C315" s="9"/>
@@ -7866,7 +7946,7 @@
       <c r="M315" s="11"/>
       <c r="N315" s="12"/>
     </row>
-    <row r="316" spans="1:14">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" s="8"/>
       <c r="B316" s="9"/>
       <c r="C316" s="9"/>
@@ -7888,7 +7968,7 @@
       <c r="M316" s="11"/>
       <c r="N316" s="12"/>
     </row>
-    <row r="317" spans="1:14">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" s="8"/>
       <c r="B317" s="9"/>
       <c r="C317" s="9"/>
@@ -7910,7 +7990,7 @@
       <c r="M317" s="11"/>
       <c r="N317" s="12"/>
     </row>
-    <row r="318" spans="1:14">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" s="8"/>
       <c r="B318" s="9"/>
       <c r="C318" s="9"/>
@@ -7932,7 +8012,7 @@
       <c r="M318" s="11"/>
       <c r="N318" s="12"/>
     </row>
-    <row r="319" spans="1:14">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A319" s="8"/>
       <c r="B319" s="9"/>
       <c r="C319" s="9"/>
@@ -7954,7 +8034,7 @@
       <c r="M319" s="11"/>
       <c r="N319" s="12"/>
     </row>
-    <row r="320" spans="1:14">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" s="8"/>
       <c r="B320" s="9"/>
       <c r="C320" s="9"/>
@@ -7976,7 +8056,7 @@
       <c r="M320" s="11"/>
       <c r="N320" s="12"/>
     </row>
-    <row r="321" spans="1:14">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A321" s="8"/>
       <c r="B321" s="9"/>
       <c r="C321" s="9"/>
@@ -7998,7 +8078,7 @@
       <c r="M321" s="11"/>
       <c r="N321" s="12"/>
     </row>
-    <row r="322" spans="1:14">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A322" s="8"/>
       <c r="B322" s="9"/>
       <c r="C322" s="9"/>
@@ -8020,7 +8100,7 @@
       <c r="M322" s="11"/>
       <c r="N322" s="12"/>
     </row>
-    <row r="323" spans="1:14">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A323" s="8"/>
       <c r="B323" s="9"/>
       <c r="C323" s="9"/>
@@ -8042,7 +8122,7 @@
       <c r="M323" s="11"/>
       <c r="N323" s="12"/>
     </row>
-    <row r="324" spans="1:14">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A324" s="8"/>
       <c r="B324" s="9"/>
       <c r="C324" s="9"/>
@@ -8064,7 +8144,7 @@
       <c r="M324" s="11"/>
       <c r="N324" s="12"/>
     </row>
-    <row r="325" spans="1:14">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A325" s="8"/>
       <c r="B325" s="9"/>
       <c r="C325" s="9"/>
@@ -8086,7 +8166,7 @@
       <c r="M325" s="11"/>
       <c r="N325" s="12"/>
     </row>
-    <row r="326" spans="1:14">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A326" s="8"/>
       <c r="B326" s="9"/>
       <c r="C326" s="9"/>
@@ -8108,7 +8188,7 @@
       <c r="M326" s="11"/>
       <c r="N326" s="12"/>
     </row>
-    <row r="327" spans="1:14">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A327" s="8"/>
       <c r="B327" s="9"/>
       <c r="C327" s="9"/>
@@ -8130,7 +8210,7 @@
       <c r="M327" s="11"/>
       <c r="N327" s="12"/>
     </row>
-    <row r="328" spans="1:14">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A328" s="8"/>
       <c r="B328" s="9"/>
       <c r="C328" s="9"/>
@@ -8152,7 +8232,7 @@
       <c r="M328" s="11"/>
       <c r="N328" s="12"/>
     </row>
-    <row r="329" spans="1:14">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A329" s="8"/>
       <c r="B329" s="9"/>
       <c r="C329" s="9"/>
@@ -8174,7 +8254,7 @@
       <c r="M329" s="11"/>
       <c r="N329" s="12"/>
     </row>
-    <row r="330" spans="1:14">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A330" s="8"/>
       <c r="B330" s="9"/>
       <c r="C330" s="9"/>
@@ -8196,7 +8276,7 @@
       <c r="M330" s="11"/>
       <c r="N330" s="12"/>
     </row>
-    <row r="331" spans="1:14">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A331" s="8"/>
       <c r="B331" s="9"/>
       <c r="C331" s="9"/>
@@ -8218,7 +8298,7 @@
       <c r="M331" s="11"/>
       <c r="N331" s="12"/>
     </row>
-    <row r="332" spans="1:14">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A332" s="8"/>
       <c r="B332" s="9"/>
       <c r="C332" s="9"/>
@@ -8240,7 +8320,7 @@
       <c r="M332" s="11"/>
       <c r="N332" s="12"/>
     </row>
-    <row r="333" spans="1:14">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A333" s="8"/>
       <c r="B333" s="9"/>
       <c r="C333" s="9"/>
@@ -8262,7 +8342,7 @@
       <c r="M333" s="11"/>
       <c r="N333" s="12"/>
     </row>
-    <row r="334" spans="1:14">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A334" s="8"/>
       <c r="B334" s="9"/>
       <c r="C334" s="9"/>
@@ -8284,7 +8364,7 @@
       <c r="M334" s="11"/>
       <c r="N334" s="12"/>
     </row>
-    <row r="335" spans="1:14">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A335" s="8"/>
       <c r="B335" s="9"/>
       <c r="C335" s="9"/>
@@ -8306,7 +8386,7 @@
       <c r="M335" s="11"/>
       <c r="N335" s="12"/>
     </row>
-    <row r="336" spans="1:14">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A336" s="8"/>
       <c r="B336" s="9"/>
       <c r="C336" s="9"/>
@@ -8328,7 +8408,7 @@
       <c r="M336" s="11"/>
       <c r="N336" s="12"/>
     </row>
-    <row r="337" spans="1:14">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A337" s="8"/>
       <c r="B337" s="9"/>
       <c r="C337" s="9"/>
@@ -8350,7 +8430,7 @@
       <c r="M337" s="11"/>
       <c r="N337" s="12"/>
     </row>
-    <row r="338" spans="1:14">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A338" s="8"/>
       <c r="B338" s="9"/>
       <c r="C338" s="9"/>
@@ -8372,7 +8452,7 @@
       <c r="M338" s="11"/>
       <c r="N338" s="12"/>
     </row>
-    <row r="339" spans="1:14">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A339" s="8"/>
       <c r="B339" s="9"/>
       <c r="C339" s="9"/>
@@ -8394,7 +8474,7 @@
       <c r="M339" s="11"/>
       <c r="N339" s="12"/>
     </row>
-    <row r="340" spans="1:14">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A340" s="8"/>
       <c r="B340" s="9"/>
       <c r="C340" s="9"/>
@@ -8416,7 +8496,7 @@
       <c r="M340" s="11"/>
       <c r="N340" s="12"/>
     </row>
-    <row r="341" spans="1:14">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A341" s="8"/>
       <c r="B341" s="9"/>
       <c r="C341" s="9"/>
@@ -8438,7 +8518,7 @@
       <c r="M341" s="11"/>
       <c r="N341" s="12"/>
     </row>
-    <row r="342" spans="1:14">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A342" s="8"/>
       <c r="B342" s="9"/>
       <c r="C342" s="9"/>
@@ -8460,7 +8540,7 @@
       <c r="M342" s="11"/>
       <c r="N342" s="12"/>
     </row>
-    <row r="343" spans="1:14">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A343" s="8"/>
       <c r="B343" s="9"/>
       <c r="C343" s="9"/>
@@ -8482,7 +8562,7 @@
       <c r="M343" s="11"/>
       <c r="N343" s="12"/>
     </row>
-    <row r="344" spans="1:14">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A344" s="8"/>
       <c r="B344" s="9"/>
       <c r="C344" s="9"/>
@@ -8504,7 +8584,7 @@
       <c r="M344" s="11"/>
       <c r="N344" s="12"/>
     </row>
-    <row r="345" spans="1:14">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A345" s="8"/>
       <c r="B345" s="9"/>
       <c r="C345" s="9"/>
@@ -8526,7 +8606,7 @@
       <c r="M345" s="11"/>
       <c r="N345" s="12"/>
     </row>
-    <row r="346" spans="1:14">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A346" s="8"/>
       <c r="B346" s="9"/>
       <c r="C346" s="9"/>
@@ -8548,7 +8628,7 @@
       <c r="M346" s="11"/>
       <c r="N346" s="12"/>
     </row>
-    <row r="347" spans="1:14">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A347" s="8"/>
       <c r="B347" s="9"/>
       <c r="C347" s="9"/>
@@ -8570,7 +8650,7 @@
       <c r="M347" s="11"/>
       <c r="N347" s="12"/>
     </row>
-    <row r="348" spans="1:14">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A348" s="8"/>
       <c r="B348" s="9"/>
       <c r="C348" s="9"/>
@@ -8592,7 +8672,7 @@
       <c r="M348" s="11"/>
       <c r="N348" s="12"/>
     </row>
-    <row r="349" spans="1:14">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A349" s="8"/>
       <c r="B349" s="9"/>
       <c r="C349" s="9"/>
@@ -8614,7 +8694,7 @@
       <c r="M349" s="11"/>
       <c r="N349" s="12"/>
     </row>
-    <row r="350" spans="1:14">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A350" s="8"/>
       <c r="B350" s="9"/>
       <c r="C350" s="9"/>
@@ -8636,7 +8716,7 @@
       <c r="M350" s="11"/>
       <c r="N350" s="12"/>
     </row>
-    <row r="351" spans="1:14">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A351" s="8"/>
       <c r="B351" s="9"/>
       <c r="C351" s="9"/>
@@ -8658,7 +8738,7 @@
       <c r="M351" s="11"/>
       <c r="N351" s="12"/>
     </row>
-    <row r="352" spans="1:14">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A352" s="8"/>
       <c r="B352" s="9"/>
       <c r="C352" s="9"/>
@@ -8680,7 +8760,7 @@
       <c r="M352" s="11"/>
       <c r="N352" s="12"/>
     </row>
-    <row r="353" spans="1:14">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A353" s="8"/>
       <c r="B353" s="9"/>
       <c r="C353" s="9"/>
@@ -8702,7 +8782,7 @@
       <c r="M353" s="11"/>
       <c r="N353" s="12"/>
     </row>
-    <row r="354" spans="1:14">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A354" s="8"/>
       <c r="B354" s="9"/>
       <c r="C354" s="9"/>
@@ -8724,7 +8804,7 @@
       <c r="M354" s="11"/>
       <c r="N354" s="12"/>
     </row>
-    <row r="355" spans="1:14">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A355" s="8"/>
       <c r="B355" s="9"/>
       <c r="C355" s="9"/>
@@ -8746,7 +8826,7 @@
       <c r="M355" s="11"/>
       <c r="N355" s="12"/>
     </row>
-    <row r="356" spans="1:14">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A356" s="8"/>
       <c r="B356" s="9"/>
       <c r="C356" s="9"/>
@@ -8768,7 +8848,7 @@
       <c r="M356" s="11"/>
       <c r="N356" s="12"/>
     </row>
-    <row r="357" spans="1:14">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A357" s="8"/>
       <c r="B357" s="9"/>
       <c r="C357" s="9"/>
@@ -8790,7 +8870,7 @@
       <c r="M357" s="11"/>
       <c r="N357" s="12"/>
     </row>
-    <row r="358" spans="1:14">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A358" s="8"/>
       <c r="B358" s="9"/>
       <c r="C358" s="9"/>
@@ -8812,7 +8892,7 @@
       <c r="M358" s="11"/>
       <c r="N358" s="12"/>
     </row>
-    <row r="359" spans="1:14">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A359" s="8"/>
       <c r="B359" s="9"/>
       <c r="C359" s="9"/>
@@ -8834,7 +8914,7 @@
       <c r="M359" s="11"/>
       <c r="N359" s="12"/>
     </row>
-    <row r="360" spans="1:14">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A360" s="8"/>
       <c r="B360" s="9"/>
       <c r="C360" s="9"/>
@@ -8856,7 +8936,7 @@
       <c r="M360" s="11"/>
       <c r="N360" s="12"/>
     </row>
-    <row r="361" spans="1:14">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A361" s="8"/>
       <c r="B361" s="9"/>
       <c r="C361" s="9"/>
@@ -8878,7 +8958,7 @@
       <c r="M361" s="11"/>
       <c r="N361" s="12"/>
     </row>
-    <row r="362" spans="1:14">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A362" s="8"/>
       <c r="B362" s="9"/>
       <c r="C362" s="9"/>
@@ -8900,7 +8980,7 @@
       <c r="M362" s="11"/>
       <c r="N362" s="12"/>
     </row>
-    <row r="363" spans="1:14">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A363" s="8"/>
       <c r="B363" s="9"/>
       <c r="C363" s="9"/>
@@ -8922,7 +9002,7 @@
       <c r="M363" s="11"/>
       <c r="N363" s="12"/>
     </row>
-    <row r="364" spans="1:14">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A364" s="8"/>
       <c r="B364" s="9"/>
       <c r="C364" s="9"/>
@@ -8944,7 +9024,7 @@
       <c r="M364" s="11"/>
       <c r="N364" s="12"/>
     </row>
-    <row r="365" spans="1:14">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A365" s="8"/>
       <c r="B365" s="9"/>
       <c r="C365" s="9"/>
@@ -8966,7 +9046,7 @@
       <c r="M365" s="11"/>
       <c r="N365" s="12"/>
     </row>
-    <row r="366" spans="1:14">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A366" s="8"/>
       <c r="B366" s="9"/>
       <c r="C366" s="9"/>
@@ -8988,7 +9068,7 @@
       <c r="M366" s="11"/>
       <c r="N366" s="12"/>
     </row>
-    <row r="367" spans="1:14">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A367" s="8"/>
       <c r="B367" s="9"/>
       <c r="C367" s="9"/>
@@ -9010,7 +9090,7 @@
       <c r="M367" s="11"/>
       <c r="N367" s="12"/>
     </row>
-    <row r="368" spans="1:14">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A368" s="8"/>
       <c r="B368" s="9"/>
       <c r="C368" s="9"/>
@@ -9032,7 +9112,7 @@
       <c r="M368" s="11"/>
       <c r="N368" s="12"/>
     </row>
-    <row r="369" spans="1:14">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A369" s="8"/>
       <c r="B369" s="9"/>
       <c r="C369" s="9"/>
@@ -9054,7 +9134,7 @@
       <c r="M369" s="11"/>
       <c r="N369" s="12"/>
     </row>
-    <row r="370" spans="1:14">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A370" s="8"/>
       <c r="B370" s="9"/>
       <c r="C370" s="9"/>
@@ -9076,7 +9156,7 @@
       <c r="M370" s="11"/>
       <c r="N370" s="12"/>
     </row>
-    <row r="371" spans="1:14">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A371" s="8"/>
       <c r="B371" s="9"/>
       <c r="C371" s="9"/>
@@ -9098,7 +9178,7 @@
       <c r="M371" s="11"/>
       <c r="N371" s="12"/>
     </row>
-    <row r="372" spans="1:14">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A372" s="8"/>
       <c r="B372" s="9"/>
       <c r="C372" s="9"/>
@@ -9120,7 +9200,7 @@
       <c r="M372" s="11"/>
       <c r="N372" s="12"/>
     </row>
-    <row r="373" spans="1:14">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A373" s="8"/>
       <c r="B373" s="9"/>
       <c r="C373" s="9"/>
@@ -9142,7 +9222,7 @@
       <c r="M373" s="11"/>
       <c r="N373" s="12"/>
     </row>
-    <row r="374" spans="1:14">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A374" s="8"/>
       <c r="B374" s="9"/>
       <c r="C374" s="9"/>
@@ -9164,7 +9244,7 @@
       <c r="M374" s="11"/>
       <c r="N374" s="12"/>
     </row>
-    <row r="375" spans="1:14">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A375" s="8"/>
       <c r="B375" s="9"/>
       <c r="C375" s="9"/>
@@ -9186,7 +9266,7 @@
       <c r="M375" s="11"/>
       <c r="N375" s="12"/>
     </row>
-    <row r="376" spans="1:14">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A376" s="8"/>
       <c r="B376" s="9"/>
       <c r="C376" s="9"/>
@@ -9208,7 +9288,7 @@
       <c r="M376" s="11"/>
       <c r="N376" s="12"/>
     </row>
-    <row r="377" spans="1:14">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A377" s="8"/>
       <c r="B377" s="9"/>
       <c r="C377" s="9"/>
@@ -9230,7 +9310,7 @@
       <c r="M377" s="11"/>
       <c r="N377" s="12"/>
     </row>
-    <row r="378" spans="1:14">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A378" s="8"/>
       <c r="B378" s="9"/>
       <c r="C378" s="9"/>
@@ -9252,7 +9332,7 @@
       <c r="M378" s="11"/>
       <c r="N378" s="12"/>
     </row>
-    <row r="379" spans="1:14">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A379" s="8"/>
       <c r="B379" s="9"/>
       <c r="C379" s="9"/>
@@ -9274,7 +9354,7 @@
       <c r="M379" s="11"/>
       <c r="N379" s="12"/>
     </row>
-    <row r="380" spans="1:14">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A380" s="8"/>
       <c r="B380" s="9"/>
       <c r="C380" s="9"/>
@@ -9296,7 +9376,7 @@
       <c r="M380" s="11"/>
       <c r="N380" s="12"/>
     </row>
-    <row r="381" spans="1:14">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A381" s="8"/>
       <c r="B381" s="9"/>
       <c r="C381" s="9"/>
@@ -9318,7 +9398,7 @@
       <c r="M381" s="11"/>
       <c r="N381" s="12"/>
     </row>
-    <row r="382" spans="1:14">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A382" s="8"/>
       <c r="B382" s="9"/>
       <c r="C382" s="9"/>
@@ -9340,7 +9420,7 @@
       <c r="M382" s="11"/>
       <c r="N382" s="12"/>
     </row>
-    <row r="383" spans="1:14">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A383" s="8"/>
       <c r="B383" s="9"/>
       <c r="C383" s="9"/>
@@ -9362,7 +9442,7 @@
       <c r="M383" s="11"/>
       <c r="N383" s="12"/>
     </row>
-    <row r="384" spans="1:14">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A384" s="8"/>
       <c r="B384" s="9"/>
       <c r="C384" s="9"/>
@@ -9384,7 +9464,7 @@
       <c r="M384" s="11"/>
       <c r="N384" s="12"/>
     </row>
-    <row r="385" spans="1:14">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A385" s="8"/>
       <c r="B385" s="9"/>
       <c r="C385" s="9"/>
@@ -9406,7 +9486,7 @@
       <c r="M385" s="11"/>
       <c r="N385" s="12"/>
     </row>
-    <row r="386" spans="1:14">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A386" s="8"/>
       <c r="B386" s="9"/>
       <c r="C386" s="9"/>
@@ -9428,7 +9508,7 @@
       <c r="M386" s="11"/>
       <c r="N386" s="12"/>
     </row>
-    <row r="387" spans="1:14">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A387" s="8"/>
       <c r="B387" s="9"/>
       <c r="C387" s="9"/>
@@ -9450,7 +9530,7 @@
       <c r="M387" s="11"/>
       <c r="N387" s="12"/>
     </row>
-    <row r="388" spans="1:14">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A388" s="8"/>
       <c r="B388" s="9"/>
       <c r="C388" s="9"/>
@@ -9472,7 +9552,7 @@
       <c r="M388" s="11"/>
       <c r="N388" s="12"/>
     </row>
-    <row r="389" spans="1:14">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A389" s="8"/>
       <c r="B389" s="9"/>
       <c r="C389" s="9"/>
@@ -9482,11 +9562,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" ref="I389:I452" si="12">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
+        <f t="shared" ref="I389:I400" si="12">IF(SUM(B389:F389,H389)=0,"",SUM(B389:F389,H389))</f>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" ref="J389:J452" si="13">IF(I389="","",1440-I389)</f>
+        <f t="shared" ref="J389:J400" si="13">IF(I389="","",1440-I389)</f>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -9494,7 +9574,7 @@
       <c r="M389" s="11"/>
       <c r="N389" s="12"/>
     </row>
-    <row r="390" spans="1:14">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A390" s="8"/>
       <c r="B390" s="9"/>
       <c r="C390" s="9"/>
@@ -9516,7 +9596,7 @@
       <c r="M390" s="11"/>
       <c r="N390" s="12"/>
     </row>
-    <row r="391" spans="1:14">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A391" s="8"/>
       <c r="B391" s="9"/>
       <c r="C391" s="9"/>
@@ -9538,7 +9618,7 @@
       <c r="M391" s="11"/>
       <c r="N391" s="12"/>
     </row>
-    <row r="392" spans="1:14">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A392" s="8"/>
       <c r="B392" s="9"/>
       <c r="C392" s="9"/>
@@ -9560,7 +9640,7 @@
       <c r="M392" s="11"/>
       <c r="N392" s="12"/>
     </row>
-    <row r="393" spans="1:14">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A393" s="8"/>
       <c r="B393" s="9"/>
       <c r="C393" s="9"/>
@@ -9582,7 +9662,7 @@
       <c r="M393" s="11"/>
       <c r="N393" s="12"/>
     </row>
-    <row r="394" spans="1:14">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A394" s="8"/>
       <c r="B394" s="9"/>
       <c r="C394" s="9"/>
@@ -9604,7 +9684,7 @@
       <c r="M394" s="11"/>
       <c r="N394" s="12"/>
     </row>
-    <row r="395" spans="1:14">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A395" s="8"/>
       <c r="B395" s="9"/>
       <c r="C395" s="9"/>
@@ -9626,7 +9706,7 @@
       <c r="M395" s="11"/>
       <c r="N395" s="12"/>
     </row>
-    <row r="396" spans="1:14">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A396" s="8"/>
       <c r="B396" s="9"/>
       <c r="C396" s="9"/>
@@ -9648,7 +9728,7 @@
       <c r="M396" s="11"/>
       <c r="N396" s="12"/>
     </row>
-    <row r="397" spans="1:14">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A397" s="8"/>
       <c r="B397" s="9"/>
       <c r="C397" s="9"/>
@@ -9670,7 +9750,7 @@
       <c r="M397" s="11"/>
       <c r="N397" s="12"/>
     </row>
-    <row r="398" spans="1:14">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A398" s="8"/>
       <c r="B398" s="9"/>
       <c r="C398" s="9"/>
@@ -9692,7 +9772,7 @@
       <c r="M398" s="11"/>
       <c r="N398" s="12"/>
     </row>
-    <row r="399" spans="1:14">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A399" s="8"/>
       <c r="B399" s="9"/>
       <c r="C399" s="9"/>
@@ -9714,7 +9794,7 @@
       <c r="M399" s="11"/>
       <c r="N399" s="12"/>
     </row>
-    <row r="400" spans="1:14">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A400" s="8"/>
       <c r="B400" s="9"/>
       <c r="C400" s="9"/>
@@ -9736,7 +9816,6 @@
       <c r="M400" s="11"/>
       <c r="N400" s="12"/>
     </row>
-    <row r="401" ht="15"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B9A733B-B549-47A5-8DCE-EA05C58CC23B}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{174B351B-74BA-4249-941A-EAADEE587E4F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1217,7 +1217,7 @@
         <v>46256</v>
       </c>
       <c r="B11" s="9">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="C11" s="9">
         <v>100</v>
@@ -1239,11 +1239,11 @@
       </c>
       <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v>880</v>
+        <v>520</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v>560</v>
+        <v>920</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>53</v>
@@ -1259,48 +1259,96 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
+      <c r="A12" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B12" s="9">
+        <v>480</v>
+      </c>
+      <c r="C12" s="9">
+        <v>90</v>
+      </c>
+      <c r="D12" s="9">
+        <v>30</v>
+      </c>
+      <c r="E12" s="9">
+        <v>10</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>360</v>
+      </c>
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
+        <v>970</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="12"/>
+        <v>470</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
+      <c r="A13" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B13" s="9">
+        <v>420</v>
+      </c>
+      <c r="C13" s="9">
+        <v>120</v>
+      </c>
+      <c r="D13" s="9">
+        <v>120</v>
+      </c>
+      <c r="E13" s="9">
+        <v>60</v>
+      </c>
+      <c r="F13" s="9">
+        <v>300</v>
+      </c>
+      <c r="G13" s="9">
+        <v>6</v>
+      </c>
+      <c r="H13" s="9">
+        <v>200</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
+        <v>220</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{174B351B-74BA-4249-941A-EAADEE587E4F}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{591DCB37-9163-4306-9D9C-C222C0BACB03}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>206-08-27</t>
+  </si>
+  <si>
+    <t>Stressed</t>
   </si>
 </sst>
 </file>
@@ -1351,92 +1357,188 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
+      <c r="A14" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B14" s="9">
+        <v>400</v>
+      </c>
+      <c r="C14" s="9">
+        <v>30</v>
+      </c>
+      <c r="D14" s="9">
+        <v>160</v>
+      </c>
+      <c r="E14" s="9">
+        <v>30</v>
+      </c>
+      <c r="F14" s="9">
+        <v>200</v>
+      </c>
+      <c r="G14" s="9">
+        <v>4</v>
+      </c>
+      <c r="H14" s="9">
+        <v>200</v>
+      </c>
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
+        <v>420</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+      <c r="A15" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B15" s="9">
+        <v>480</v>
+      </c>
+      <c r="C15" s="9">
+        <v>30</v>
+      </c>
+      <c r="D15" s="9">
+        <v>120</v>
+      </c>
+      <c r="E15" s="9">
+        <v>60</v>
+      </c>
+      <c r="F15" s="9">
+        <v>400</v>
+      </c>
+      <c r="G15" s="9">
+        <v>8</v>
+      </c>
+      <c r="H15" s="9">
+        <v>300</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+      <c r="A16" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="9">
+        <v>360</v>
+      </c>
+      <c r="C16" s="9">
+        <v>40</v>
+      </c>
+      <c r="D16" s="9">
+        <v>120</v>
+      </c>
+      <c r="E16" s="9">
+        <v>30</v>
+      </c>
+      <c r="F16" s="9">
+        <v>200</v>
+      </c>
+      <c r="G16" s="9">
+        <v>4</v>
+      </c>
+      <c r="H16" s="9">
+        <v>200</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
+        <v>490</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+      <c r="A17" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B17" s="9">
+        <v>400</v>
+      </c>
+      <c r="C17" s="9">
+        <v>30</v>
+      </c>
+      <c r="D17" s="9">
+        <v>300</v>
+      </c>
+      <c r="E17" s="9">
+        <v>120</v>
+      </c>
+      <c r="F17" s="9">
+        <v>250</v>
+      </c>
+      <c r="G17" s="9">
+        <v>5</v>
+      </c>
+      <c r="H17" s="9">
+        <v>200</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
+        <v>140</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{591DCB37-9163-4306-9D9C-C222C0BACB03}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46FAA201-C5BD-433B-B8C9-ED71BA319D2F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>Stressed</t>
+  </si>
+  <si>
+    <t>Suffering from Fever</t>
+  </si>
+  <si>
+    <t>Feeling better than yesterday</t>
   </si>
 </sst>
 </file>
@@ -1541,70 +1547,142 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+      <c r="A18" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B18" s="9">
+        <v>420</v>
+      </c>
+      <c r="C18" s="9">
+        <v>10</v>
+      </c>
+      <c r="D18" s="9">
+        <v>30</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>400</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>860</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+        <v>580</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
+      <c r="A19" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B19" s="9">
+        <v>480</v>
+      </c>
+      <c r="C19" s="9">
+        <v>15</v>
+      </c>
+      <c r="D19" s="9">
+        <v>50</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>300</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>845</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
+        <v>595</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
+      <c r="A20" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B20" s="9">
+        <v>400</v>
+      </c>
+      <c r="C20" s="9">
+        <v>30</v>
+      </c>
+      <c r="D20" s="9">
+        <v>180</v>
+      </c>
+      <c r="E20" s="9">
+        <v>200</v>
+      </c>
+      <c r="F20" s="9">
+        <v>300</v>
+      </c>
+      <c r="G20" s="9">
+        <v>6</v>
+      </c>
+      <c r="H20" s="9">
+        <v>300</v>
+      </c>
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
+        <v>30</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46FAA201-C5BD-433B-B8C9-ED71BA319D2F}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DC78E9B-B3A3-4363-83C7-8E4E84D9147D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,27 @@
   </si>
   <si>
     <t>Feeling better than yesterday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holiday </t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Good Day</t>
+  </si>
+  <si>
+    <t>Haptic Schedule</t>
+  </si>
+  <si>
+    <t>Neutral day</t>
+  </si>
+  <si>
+    <t>Enjoyed</t>
   </si>
 </sst>
 </file>
@@ -1685,136 +1706,280 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
+      <c r="A21" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B21" s="9">
+        <v>300</v>
+      </c>
+      <c r="C21" s="9">
+        <v>30</v>
+      </c>
+      <c r="D21" s="9">
+        <v>300</v>
+      </c>
+      <c r="E21" s="9">
+        <v>100</v>
+      </c>
+      <c r="F21" s="9">
+        <v>200</v>
+      </c>
+      <c r="G21" s="9">
+        <v>4</v>
+      </c>
+      <c r="H21" s="9">
+        <v>400</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
+        <v>110</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
+      <c r="A22" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="9">
+        <v>360</v>
+      </c>
+      <c r="C22" s="9">
+        <v>40</v>
+      </c>
+      <c r="D22" s="9">
+        <v>200</v>
+      </c>
+      <c r="E22" s="9">
+        <v>60</v>
+      </c>
+      <c r="F22" s="9">
+        <v>400</v>
+      </c>
+      <c r="G22" s="9">
+        <v>8</v>
+      </c>
+      <c r="H22" s="9">
+        <v>300</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
+        <v>80</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
+      <c r="A23" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="9">
+        <v>420</v>
+      </c>
+      <c r="C23" s="9">
+        <v>20</v>
+      </c>
+      <c r="D23" s="9">
+        <v>250</v>
+      </c>
+      <c r="E23" s="9">
+        <v>45</v>
+      </c>
+      <c r="F23" s="9">
+        <v>200</v>
+      </c>
+      <c r="G23" s="9">
+        <v>4</v>
+      </c>
+      <c r="H23" s="9">
+        <v>240</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
+        <v>265</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
+      <c r="A24" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B24" s="9">
+        <v>360</v>
+      </c>
+      <c r="C24" s="9">
+        <v>45</v>
+      </c>
+      <c r="D24" s="9">
+        <v>140</v>
+      </c>
+      <c r="E24" s="9">
+        <v>100</v>
+      </c>
+      <c r="F24" s="9">
+        <v>250</v>
+      </c>
+      <c r="G24" s="9">
+        <v>5</v>
+      </c>
+      <c r="H24" s="9">
+        <v>200</v>
+      </c>
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
+        <v>345</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
+      <c r="A25" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B25" s="9">
+        <v>180</v>
+      </c>
+      <c r="C25" s="9">
+        <v>60</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>540</v>
+      </c>
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
+        <v>780</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="12"/>
+        <v>660</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
+      <c r="A26" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B26" s="9">
+        <v>540</v>
+      </c>
+      <c r="C26" s="9">
+        <v>20</v>
+      </c>
+      <c r="D26" s="9">
+        <v>120</v>
+      </c>
+      <c r="E26" s="9">
+        <v>30</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>540</v>
+      </c>
+      <c r="I26" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12"/>
+        <v>190</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30508"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DC78E9B-B3A3-4363-83C7-8E4E84D9147D}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF5B31E0-EDA2-474C-A227-056089B528A0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,18 @@
   </si>
   <si>
     <t>Enjoyed</t>
+  </si>
+  <si>
+    <t>Haptic day</t>
+  </si>
+  <si>
+    <t>Netural</t>
+  </si>
+  <si>
+    <t>neutral day</t>
+  </si>
+  <si>
+    <t>Good day</t>
   </si>
 </sst>
 </file>
@@ -1982,114 +1994,234 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
+      <c r="A27" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="9">
+        <v>320</v>
+      </c>
+      <c r="C27" s="9">
+        <v>30</v>
+      </c>
+      <c r="D27" s="9">
+        <v>200</v>
+      </c>
+      <c r="E27" s="9">
+        <v>60</v>
+      </c>
+      <c r="F27" s="9">
+        <v>300</v>
+      </c>
+      <c r="G27" s="9">
+        <v>6</v>
+      </c>
+      <c r="H27" s="9">
+        <v>320</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
+        <v>210</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
+      <c r="A28" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B28" s="9">
+        <v>480</v>
+      </c>
+      <c r="C28" s="9">
+        <v>45</v>
+      </c>
+      <c r="D28" s="9">
+        <v>300</v>
+      </c>
+      <c r="E28" s="9">
+        <v>80</v>
+      </c>
+      <c r="F28" s="9">
+        <v>200</v>
+      </c>
+      <c r="G28" s="9">
+        <v>4</v>
+      </c>
+      <c r="H28" s="9">
+        <v>320</v>
+      </c>
+      <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
+        <v>1425</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="12"/>
+        <v>15</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
+      <c r="A29" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B29" s="9">
+        <v>520</v>
+      </c>
+      <c r="C29" s="9">
+        <v>20</v>
+      </c>
+      <c r="D29" s="9">
+        <v>240</v>
+      </c>
+      <c r="E29" s="9">
+        <v>90</v>
+      </c>
+      <c r="F29" s="9">
+        <v>400</v>
+      </c>
+      <c r="G29" s="9">
+        <v>8</v>
+      </c>
+      <c r="H29" s="9">
+        <v>120</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
+      <c r="A30" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B30" s="9">
+        <v>500</v>
+      </c>
+      <c r="C30" s="9">
+        <v>35</v>
+      </c>
+      <c r="D30" s="9">
+        <v>460</v>
+      </c>
+      <c r="E30" s="9">
+        <v>60</v>
+      </c>
+      <c r="F30" s="9">
+        <v>200</v>
+      </c>
+      <c r="G30" s="9">
+        <v>4</v>
+      </c>
+      <c r="H30" s="9">
+        <v>120</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
+        <v>1375</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
+        <v>65</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+      <c r="A31" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B31" s="9">
+        <v>340</v>
+      </c>
+      <c r="C31" s="9">
+        <v>45</v>
+      </c>
+      <c r="D31" s="9">
+        <v>400</v>
+      </c>
+      <c r="E31" s="9">
+        <v>90</v>
+      </c>
+      <c r="F31" s="9">
+        <v>250</v>
+      </c>
+      <c r="G31" s="9">
+        <v>5</v>
+      </c>
+      <c r="H31" s="9">
+        <v>110</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>1235</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+        <v>205</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF5B31E0-EDA2-474C-A227-056089B528A0}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35308A20-D445-45A2-97C3-B1666ECE9F45}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Good day</t>
+  </si>
+  <si>
+    <t>Just gone to Bed at 3Am after study and wake at 10 Am</t>
   </si>
 </sst>
 </file>
@@ -2223,27 +2226,51 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="10" t="str">
+    <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
+        <v>46277</v>
+      </c>
+      <c r="B32" s="9">
+        <v>450</v>
+      </c>
+      <c r="C32" s="9">
+        <v>10</v>
+      </c>
+      <c r="D32" s="9">
+        <v>300</v>
+      </c>
+      <c r="E32" s="9">
+        <v>120</v>
+      </c>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
+        <v>300</v>
+      </c>
+      <c r="I32" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="10" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J32" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="11"/>
-      <c r="N32" s="12"/>
+        <v>260</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M32" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35308A20-D445-45A2-97C3-B1666ECE9F45}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94100A83-EAEA-42E3-B120-1FAD9EF65774}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,12 @@
   </si>
   <si>
     <t>Just gone to Bed at 3Am after study and wake at 10 Am</t>
+  </si>
+  <si>
+    <t>Studying for upcoming CA</t>
+  </si>
+  <si>
+    <t>CA of Python</t>
   </si>
 </sst>
 </file>
@@ -2273,70 +2279,142 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="10" t="str">
+      <c r="A33" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="9">
+        <v>420</v>
+      </c>
+      <c r="C33" s="9">
+        <v>60</v>
+      </c>
+      <c r="D33" s="9">
+        <v>360</v>
+      </c>
+      <c r="E33" s="9">
+        <v>90</v>
+      </c>
+      <c r="F33" s="9">
+        <v>0</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9">
+        <v>510</v>
+      </c>
+      <c r="I33" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="10" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L33" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="10" t="str">
+      <c r="A34" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="9">
+        <v>420</v>
+      </c>
+      <c r="C34" s="9">
+        <v>70</v>
+      </c>
+      <c r="D34" s="9">
+        <v>120</v>
+      </c>
+      <c r="E34" s="9">
+        <v>60</v>
+      </c>
+      <c r="F34" s="9">
+        <v>300</v>
+      </c>
+      <c r="G34" s="9">
+        <v>6</v>
+      </c>
+      <c r="H34" s="9">
+        <v>420</v>
+      </c>
+      <c r="I34" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="10" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
-      <c r="M34" s="11"/>
-      <c r="N34" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="N34" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="10" t="str">
+      <c r="A35" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="9">
+        <v>480</v>
+      </c>
+      <c r="C35" s="9">
+        <v>50</v>
+      </c>
+      <c r="D35" s="9">
+        <v>60</v>
+      </c>
+      <c r="E35" s="9">
+        <v>20</v>
+      </c>
+      <c r="F35" s="9">
+        <v>200</v>
+      </c>
+      <c r="G35" s="9">
+        <v>4</v>
+      </c>
+      <c r="H35" s="9">
+        <v>400</v>
+      </c>
+      <c r="I35" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="10" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
+        <v>230</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N35" s="12" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30508"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30515"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94100A83-EAEA-42E3-B120-1FAD9EF65774}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A57479B6-14E5-4671-98A0-3910D6AA31AA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -168,36 +168,6 @@
     <t>Fitness (min)</t>
   </si>
   <si>
-    <t>Study (min)</t>
-  </si>
-  <si>
-    <t>Coding (min)</t>
-  </si>
-  <si>
-    <t>Class (min)</t>
-  </si>
-  <si>
-    <t>Classes Attended</t>
-  </si>
-  <si>
-    <t>Other Activities (min)</t>
-  </si>
-  <si>
-    <t>Total Tracked (min)</t>
-  </si>
-  <si>
-    <t>Free/Unaccounted (min)</t>
-  </si>
-  <si>
-    <t>Day's Feeling</t>
-  </si>
-  <si>
-    <t>Satisfaction Level</t>
-  </si>
-  <si>
-    <t>Energy Level</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -280,6 +250,45 @@
   </si>
   <si>
     <t>CA of Python</t>
+  </si>
+  <si>
+    <t>Study_min</t>
+  </si>
+  <si>
+    <t>Coding_min</t>
+  </si>
+  <si>
+    <t>Class_min</t>
+  </si>
+  <si>
+    <t>Classes_Attended</t>
+  </si>
+  <si>
+    <t>Other_Activities_min</t>
+  </si>
+  <si>
+    <t>Total_Tracked_min</t>
+  </si>
+  <si>
+    <t>Free_Unaccounted_min</t>
+  </si>
+  <si>
+    <t>Day_Feeling</t>
+  </si>
+  <si>
+    <t>Satisfaction_Level</t>
+  </si>
+  <si>
+    <t>Energy_Level</t>
+  </si>
+  <si>
+    <t>Preparing for CA of Anylatical</t>
+  </si>
+  <si>
+    <t>Today I am Tired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lots of pressure due to the ca of Anylastical its getting to complicated </t>
   </si>
 </sst>
 </file>
@@ -384,7 +393,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -407,11 +416,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -436,6 +456,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -923,76 +946,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <v>12605718</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
       <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="16"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-    </row>
-    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+    </row>
+    <row r="5" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>39</v>
       </c>
@@ -1003,37 +1026,37 @@
         <v>41</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -1070,16 +1093,16 @@
         <v>390</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1116,16 +1139,16 @@
         <v>150</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N7" s="12" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1162,16 +1185,16 @@
         <v>148</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N8" s="12" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1208,16 +1231,16 @@
         <v>430</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="N9" s="12" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1254,16 +1277,16 @@
         <v>250</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1300,16 +1323,16 @@
         <v>920</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1346,16 +1369,16 @@
         <v>470</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1392,16 +1415,16 @@
         <v>220</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="N13" s="12" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1438,16 +1461,16 @@
         <v>420</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1484,21 +1507,21 @@
         <v>50</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B16" s="9">
         <v>360</v>
@@ -1530,16 +1553,16 @@
         <v>490</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N16" s="12" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1576,16 +1599,16 @@
         <v>140</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N17" s="12" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1622,16 +1645,16 @@
         <v>580</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1668,16 +1691,16 @@
         <v>595</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1714,16 +1737,16 @@
         <v>30</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M20" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N20" s="12" t="s">
         <v>55</v>
-      </c>
-      <c r="N20" s="12" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1760,16 +1783,16 @@
         <v>110</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1806,16 +1829,16 @@
         <v>80</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1852,16 +1875,16 @@
         <v>265</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1898,16 +1921,16 @@
         <v>345</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -1944,16 +1967,16 @@
         <v>660</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -1990,16 +2013,16 @@
         <v>190</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2036,16 +2059,16 @@
         <v>210</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2082,16 +2105,16 @@
         <v>15</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2128,16 +2151,16 @@
         <v>50</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2174,16 +2197,16 @@
         <v>65</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2220,16 +2243,16 @@
         <v>205</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2266,16 +2289,16 @@
         <v>260</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2312,16 +2335,16 @@
         <v>0</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2358,16 +2381,16 @@
         <v>50</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2404,83 +2427,155 @@
         <v>230</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
-      <c r="H36" s="9"/>
-      <c r="I36" s="10" t="str">
+      <c r="A36" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="9">
+        <v>360</v>
+      </c>
+      <c r="C36" s="9">
+        <v>30</v>
+      </c>
+      <c r="D36" s="9">
+        <v>300</v>
+      </c>
+      <c r="E36" s="9">
+        <v>40</v>
+      </c>
+      <c r="F36" s="9">
+        <v>400</v>
+      </c>
+      <c r="G36" s="9">
+        <v>8</v>
+      </c>
+      <c r="H36" s="9">
+        <v>200</v>
+      </c>
+      <c r="I36" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="10" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J36" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="12"/>
+        <v>110</v>
+      </c>
+      <c r="K36" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M36" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N36" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
-      <c r="I37" s="10" t="str">
+      <c r="A37" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B37" s="9">
+        <v>300</v>
+      </c>
+      <c r="C37" s="9">
+        <v>40</v>
+      </c>
+      <c r="D37" s="9">
+        <v>540</v>
+      </c>
+      <c r="E37" s="13">
+        <v>120</v>
+      </c>
+      <c r="F37" s="9">
+        <v>200</v>
+      </c>
+      <c r="G37" s="9">
+        <v>4</v>
+      </c>
+      <c r="H37" s="9">
+        <v>240</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="10" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="12"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="10" t="str">
+        <v>0</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L37" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M37" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N37" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B38" s="9">
+        <v>180</v>
+      </c>
+      <c r="C38" s="9">
+        <v>30</v>
+      </c>
+      <c r="D38" s="9">
+        <v>600</v>
+      </c>
+      <c r="E38" s="9">
+        <v>30</v>
+      </c>
+      <c r="F38" s="9">
+        <v>250</v>
+      </c>
+      <c r="G38" s="9">
+        <v>5</v>
+      </c>
+      <c r="H38" s="9">
+        <v>240</v>
+      </c>
+      <c r="I38" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="10" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J38" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="12"/>
+        <v>110</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N38" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A57479B6-14E5-4671-98A0-3910D6AA31AA}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDF5405F-9705-423A-8C53-66A6C28916D0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t xml:space="preserve">lots of pressure due to the ca of Anylastical its getting to complicated </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA of Analytical Completed </t>
   </si>
 </sst>
 </file>
@@ -2578,26 +2581,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="10" t="str">
+      <c r="A39" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B39" s="9">
+        <v>540</v>
+      </c>
+      <c r="C39" s="9">
+        <v>35</v>
+      </c>
+      <c r="D39" s="9">
+        <v>480</v>
+      </c>
+      <c r="E39" s="9">
+        <v>30</v>
+      </c>
+      <c r="F39" s="9">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9">
+        <v>250</v>
+      </c>
+      <c r="I39" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="10" t="str">
+        <v>1335</v>
+      </c>
+      <c r="J39" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="12"/>
+        <v>105</v>
+      </c>
+      <c r="K39" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L39" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M39" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N39" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="126" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDF5405F-9705-423A-8C53-66A6C28916D0}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3CF1740-41BC-42AB-BB70-BCF8131277B6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t xml:space="preserve">CA of Analytical Completed </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enjoyed the Birthday Party of my Friend</t>
   </si>
 </sst>
 </file>
@@ -2626,27 +2629,51 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10" t="str">
+    <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B40" s="9">
+        <v>300</v>
+      </c>
+      <c r="C40" s="9">
+        <v>30</v>
+      </c>
+      <c r="D40" s="9">
+        <v>120</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9">
+        <v>0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>500</v>
+      </c>
+      <c r="I40" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J40" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
+        <v>490</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30515"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30520"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3CF1740-41BC-42AB-BB70-BCF8131277B6}"/>
+  <xr:revisionPtr revIDLastSave="152" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE08FC83-AA83-4BDE-B9ED-F9E246326348}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve"> Enjoyed the Birthday Party of my Friend</t>
+  </si>
+  <si>
+    <t>CA of DBMS is not gone good</t>
   </si>
 </sst>
 </file>
@@ -2676,26 +2679,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
+      <c r="A41" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B41" s="9">
+        <v>360</v>
+      </c>
+      <c r="C41" s="9">
+        <v>40</v>
+      </c>
+      <c r="D41" s="9">
+        <v>280</v>
+      </c>
+      <c r="E41" s="9">
+        <v>30</v>
+      </c>
+      <c r="F41" s="9">
+        <v>300</v>
+      </c>
+      <c r="G41" s="9">
+        <v>6</v>
+      </c>
+      <c r="H41" s="9">
+        <v>420</v>
+      </c>
+      <c r="I41" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J41" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE08FC83-AA83-4BDE-B9ED-F9E246326348}"/>
+  <xr:revisionPtr revIDLastSave="153" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{972D5A2D-E549-4D1E-BDE2-A5B6D8267781}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,15 @@
   </si>
   <si>
     <t>CA of DBMS is not gone good</t>
+  </si>
+  <si>
+    <t>Normal day</t>
+  </si>
+  <si>
+    <t>Hedache at Night</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Just a good day </t>
   </si>
 </sst>
 </file>
@@ -2725,70 +2734,142 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
+      <c r="A42" s="8">
+        <v>46287</v>
+      </c>
+      <c r="B42" s="9">
+        <v>300</v>
+      </c>
+      <c r="C42" s="9">
+        <v>60</v>
+      </c>
+      <c r="D42" s="9">
+        <v>120</v>
+      </c>
+      <c r="E42" s="9">
+        <v>45</v>
+      </c>
+      <c r="F42" s="9">
+        <v>200</v>
+      </c>
+      <c r="G42" s="9">
+        <v>4</v>
+      </c>
+      <c r="H42" s="9">
+        <v>560</v>
+      </c>
+      <c r="I42" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
+        <v>1285</v>
+      </c>
+      <c r="J42" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
+        <v>155</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
+      <c r="A43" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="9">
+        <v>360</v>
+      </c>
+      <c r="C43" s="9">
+        <v>45</v>
+      </c>
+      <c r="D43" s="9">
+        <v>180</v>
+      </c>
+      <c r="E43" s="9">
+        <v>30</v>
+      </c>
+      <c r="F43" s="9">
+        <v>400</v>
+      </c>
+      <c r="G43" s="9">
+        <v>8</v>
+      </c>
+      <c r="H43" s="9">
+        <v>420</v>
+      </c>
+      <c r="I43" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
+        <v>1435</v>
+      </c>
+      <c r="J43" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
+        <v>5</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
+      <c r="A44" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="9">
+        <v>480</v>
+      </c>
+      <c r="C44" s="9">
+        <v>120</v>
+      </c>
+      <c r="D44" s="9">
+        <v>360</v>
+      </c>
+      <c r="E44" s="9">
+        <v>60</v>
+      </c>
+      <c r="F44" s="9">
+        <v>200</v>
+      </c>
+      <c r="G44" s="9">
+        <v>4</v>
+      </c>
+      <c r="H44" s="9">
+        <v>220</v>
+      </c>
+      <c r="I44" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J44" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30520"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="153" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{972D5A2D-E549-4D1E-BDE2-A5B6D8267781}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56D51F9E-4BA2-46B1-B3DA-60384BC72D48}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +307,24 @@
   </si>
   <si>
     <t xml:space="preserve">Just a good day </t>
+  </si>
+  <si>
+    <t xml:space="preserve">There is no CA of C++ </t>
+  </si>
+  <si>
+    <t>Today I have Mentor metting and the stuation of university is going bad at night</t>
+  </si>
+  <si>
+    <t>The situation is more worst than previous day</t>
+  </si>
+  <si>
+    <t>just booked the ticket for my home</t>
+  </si>
+  <si>
+    <t>While going I got message that we have CA from 12 that news make me confused because I thought that they would take time to renovate the college</t>
+  </si>
+  <si>
+    <t>I just give surprise to my parents,arrived my home without telling anyone</t>
   </si>
 </sst>
 </file>
@@ -2872,136 +2890,274 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
+      <c r="A45" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B45" s="9">
+        <v>360</v>
+      </c>
+      <c r="C45" s="9">
+        <v>100</v>
+      </c>
+      <c r="D45" s="9">
+        <v>260</v>
+      </c>
+      <c r="E45" s="9">
+        <v>120</v>
+      </c>
+      <c r="F45" s="9">
+        <v>250</v>
+      </c>
+      <c r="G45" s="9">
+        <v>5</v>
+      </c>
+      <c r="H45" s="9">
+        <v>300</v>
+      </c>
+      <c r="I45" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J45" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
+        <v>50</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L45" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M45" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N45" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A46" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B46" s="9">
+        <v>100</v>
+      </c>
+      <c r="C46" s="9">
+        <v>160</v>
+      </c>
+      <c r="D46" s="9">
+        <v>200</v>
+      </c>
+      <c r="E46" s="9">
+        <v>30</v>
+      </c>
+      <c r="F46" s="9">
+        <v>150</v>
+      </c>
+      <c r="G46" s="9">
+        <v>3</v>
+      </c>
+      <c r="H46" s="9">
+        <v>260</v>
+      </c>
+      <c r="I46" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
+        <v>900</v>
+      </c>
+      <c r="J46" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="12"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
+        <v>540</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B47" s="9">
+        <v>200</v>
+      </c>
+      <c r="C47" s="9">
+        <v>120</v>
+      </c>
+      <c r="D47" s="9">
+        <v>0</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>600</v>
+      </c>
+      <c r="I47" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
+        <v>920</v>
+      </c>
+      <c r="J47" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
+        <v>520</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B48" s="9">
+        <v>360</v>
+      </c>
+      <c r="C48" s="9">
+        <v>60</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0</v>
+      </c>
+      <c r="E48" s="9">
+        <v>60</v>
+      </c>
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
+      <c r="I48" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="J48" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="10" t="str">
+        <v>960</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A49" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B49" s="9">
+        <v>280</v>
+      </c>
+      <c r="C49" s="9">
+        <v>45</v>
+      </c>
+      <c r="D49" s="9">
+        <v>160</v>
+      </c>
+      <c r="E49" s="9">
+        <v>100</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>500</v>
+      </c>
+      <c r="I49" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J49" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="12"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="10" t="str">
+        <v>355</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B50" s="9">
+        <v>160</v>
+      </c>
+      <c r="C50" s="9">
+        <v>40</v>
+      </c>
+      <c r="D50" s="9">
+        <v>60</v>
+      </c>
+      <c r="E50" s="9">
+        <v>0</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>400</v>
+      </c>
+      <c r="I50" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="str">
+        <v>660</v>
+      </c>
+      <c r="J50" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="12"/>
+        <v>780</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56D51F9E-4BA2-46B1-B3DA-60384BC72D48}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80DAD992-4117-434D-8E9E-55F44AC11917}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,18 @@
   </si>
   <si>
     <t>I just give surprise to my parents,arrived my home without telling anyone</t>
+  </si>
+  <si>
+    <t>i finally got to sleep peacefully at my home today</t>
+  </si>
+  <si>
+    <t>today I visited my grandfathers home</t>
+  </si>
+  <si>
+    <t>Today I just meet my friends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am searching for my ticket the ticket is not avaliable </t>
   </si>
 </sst>
 </file>
@@ -3159,93 +3171,189 @@
         <v>94</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="10" t="str">
+    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B51" s="9">
+        <v>90</v>
+      </c>
+      <c r="C51" s="9">
+        <v>20</v>
+      </c>
+      <c r="D51" s="9">
+        <v>0</v>
+      </c>
+      <c r="E51" s="9">
+        <v>0</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>500</v>
+      </c>
+      <c r="I51" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="10" t="str">
+        <v>610</v>
+      </c>
+      <c r="J51" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="12"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="10" t="str">
+        <v>830</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B52" s="9">
+        <v>120</v>
+      </c>
+      <c r="C52" s="9">
+        <v>30</v>
+      </c>
+      <c r="D52" s="9">
+        <v>120</v>
+      </c>
+      <c r="E52" s="9">
+        <v>25</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>600</v>
+      </c>
+      <c r="I52" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="10" t="str">
+        <v>895</v>
+      </c>
+      <c r="J52" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="12"/>
+        <v>545</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="10" t="str">
+      <c r="A53" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B53" s="9">
+        <v>320</v>
+      </c>
+      <c r="C53" s="9">
+        <v>40</v>
+      </c>
+      <c r="D53" s="9">
+        <v>200</v>
+      </c>
+      <c r="E53" s="9">
+        <v>50</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>780</v>
+      </c>
+      <c r="I53" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="10" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J53" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="12"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="10" t="str">
+        <v>50</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B54" s="9">
+        <v>480</v>
+      </c>
+      <c r="C54" s="9">
+        <v>35</v>
+      </c>
+      <c r="D54" s="9">
+        <v>60</v>
+      </c>
+      <c r="E54" s="9">
+        <v>30</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>680</v>
+      </c>
+      <c r="I54" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="10" t="str">
+        <v>1285</v>
+      </c>
+      <c r="J54" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="12"/>
+        <v>155</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30604"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="157" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80DAD992-4117-434D-8E9E-55F44AC11917}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CC228BB-CE67-4CE2-850E-14DF127AD1D0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -198,9 +198,6 @@
     <t>Unsatisfied</t>
   </si>
   <si>
-    <t>206-08-27</t>
-  </si>
-  <si>
     <t>Stressed</t>
   </si>
   <si>
@@ -337,6 +334,12 @@
   </si>
   <si>
     <t xml:space="preserve">I am searching for my ticket the ticket is not avaliable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our class is going online </t>
+  </si>
+  <si>
+    <t xml:space="preserve">our MTT is coming so we have to study  </t>
   </si>
 </sst>
 </file>
@@ -1074,34 +1077,34 @@
         <v>41</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="N5" s="7" t="s">
         <v>42</v>
@@ -1555,7 +1558,7 @@
         <v>50</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L15" s="11" t="s">
         <v>51</v>
@@ -1568,8 +1571,8 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>52</v>
+      <c r="A16" s="8">
+        <v>46261</v>
       </c>
       <c r="B16" s="9">
         <v>360</v>
@@ -1702,7 +1705,7 @@
         <v>47</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1748,7 +1751,7 @@
         <v>47</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1794,7 +1797,7 @@
         <v>45</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1840,7 +1843,7 @@
         <v>45</v>
       </c>
       <c r="N21" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1880,13 +1883,13 @@
         <v>43</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>47</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1978,7 +1981,7 @@
         <v>45</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2015,7 +2018,7 @@
         <v>660</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L25" s="11" t="s">
         <v>44</v>
@@ -2024,7 +2027,7 @@
         <v>45</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2061,7 +2064,7 @@
         <v>190</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L26" s="11" t="s">
         <v>51</v>
@@ -2070,7 +2073,7 @@
         <v>47</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2116,7 +2119,7 @@
         <v>45</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2153,7 +2156,7 @@
         <v>15</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L28" s="11" t="s">
         <v>46</v>
@@ -2162,7 +2165,7 @@
         <v>45</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2208,7 +2211,7 @@
         <v>47</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2254,7 +2257,7 @@
         <v>45</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2300,7 +2303,7 @@
         <v>47</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2346,7 +2349,7 @@
         <v>49</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2392,7 +2395,7 @@
         <v>47</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2438,7 +2441,7 @@
         <v>45</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2484,7 +2487,7 @@
         <v>49</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -2530,7 +2533,7 @@
         <v>47</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -2576,7 +2579,7 @@
         <v>45</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2616,13 +2619,13 @@
         <v>43</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M38" s="11" t="s">
         <v>49</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2668,7 +2671,7 @@
         <v>45</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2714,7 +2717,7 @@
         <v>45</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2760,7 +2763,7 @@
         <v>45</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -2797,7 +2800,7 @@
         <v>155</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L42" s="11" t="s">
         <v>44</v>
@@ -2806,7 +2809,7 @@
         <v>45</v>
       </c>
       <c r="N42" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -2852,7 +2855,7 @@
         <v>45</v>
       </c>
       <c r="N43" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -2898,7 +2901,7 @@
         <v>49</v>
       </c>
       <c r="N44" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -2944,7 +2947,7 @@
         <v>45</v>
       </c>
       <c r="N45" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2990,7 +2993,7 @@
         <v>45</v>
       </c>
       <c r="N46" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3036,7 +3039,7 @@
         <v>45</v>
       </c>
       <c r="N47" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3067,16 +3070,16 @@
         <v>960</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L48" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M48" s="11" t="s">
         <v>49</v>
       </c>
       <c r="N48" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -3113,16 +3116,16 @@
         <v>355</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L49" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M49" s="11" t="s">
         <v>49</v>
       </c>
       <c r="N49" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -3159,16 +3162,16 @@
         <v>780</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M50" s="11" t="s">
         <v>49</v>
       </c>
       <c r="N50" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3208,13 +3211,13 @@
         <v>46</v>
       </c>
       <c r="L51" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M51" s="11" t="s">
         <v>49</v>
       </c>
       <c r="N51" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3260,7 +3263,7 @@
         <v>45</v>
       </c>
       <c r="N52" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -3306,7 +3309,7 @@
         <v>45</v>
       </c>
       <c r="N53" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3352,52 +3355,100 @@
         <v>47</v>
       </c>
       <c r="N54" s="12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A55" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B55" s="9">
+        <v>360</v>
+      </c>
+      <c r="C55" s="9">
+        <v>40</v>
+      </c>
+      <c r="D55" s="9">
+        <v>120</v>
+      </c>
+      <c r="E55" s="9">
+        <v>60</v>
+      </c>
+      <c r="F55" s="9">
+        <v>300</v>
+      </c>
+      <c r="G55" s="9">
+        <v>5</v>
+      </c>
+      <c r="H55" s="9">
+        <v>500</v>
+      </c>
+      <c r="I55" s="10">
+        <f t="shared" si="0"/>
+        <v>1380</v>
+      </c>
+      <c r="J55" s="10">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N55" s="12" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="10" t="str">
+    <row r="56" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="9">
+        <v>300</v>
+      </c>
+      <c r="C56" s="9">
+        <v>30</v>
+      </c>
+      <c r="D56" s="9">
+        <v>90</v>
+      </c>
+      <c r="E56" s="9">
+        <v>30</v>
+      </c>
+      <c r="F56" s="9">
+        <v>200</v>
+      </c>
+      <c r="G56" s="9">
+        <v>4</v>
+      </c>
+      <c r="H56" s="9">
+        <v>480</v>
+      </c>
+      <c r="I56" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="10" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J56" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="12"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="10" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="12"/>
+        <v>310</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N56" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30604"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CC228BB-CE67-4CE2-850E-14DF127AD1D0}"/>
+  <xr:revisionPtr revIDLastSave="160" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80BA1352-2849-46D7-935F-B3439B196351}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,6 +340,15 @@
   </si>
   <si>
     <t xml:space="preserve">our MTT is coming so we have to study  </t>
+  </si>
+  <si>
+    <t>I am enjoying my time with my parents</t>
+  </si>
+  <si>
+    <t>I am trying to book by ticket but I am unable to book</t>
+  </si>
+  <si>
+    <t>i am preparing for my mtt</t>
   </si>
 </sst>
 </file>
@@ -3450,71 +3459,143 @@
         <v>99</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="10" t="str">
+    <row r="57" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="9">
+        <v>400</v>
+      </c>
+      <c r="C57" s="9">
+        <v>20</v>
+      </c>
+      <c r="D57" s="9">
+        <v>160</v>
+      </c>
+      <c r="E57" s="9">
+        <v>45</v>
+      </c>
+      <c r="F57" s="9">
+        <v>400</v>
+      </c>
+      <c r="G57" s="9">
+        <v>8</v>
+      </c>
+      <c r="H57" s="9">
+        <v>360</v>
+      </c>
+      <c r="I57" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="10" t="str">
+        <v>1385</v>
+      </c>
+      <c r="J57" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="12"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="10" t="str">
+        <v>55</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N57" s="12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="9">
+        <v>260</v>
+      </c>
+      <c r="C58" s="9">
+        <v>10</v>
+      </c>
+      <c r="D58" s="9">
+        <v>200</v>
+      </c>
+      <c r="E58" s="9">
+        <v>26</v>
+      </c>
+      <c r="F58" s="9">
+        <v>0</v>
+      </c>
+      <c r="G58" s="9">
+        <v>0</v>
+      </c>
+      <c r="H58" s="9">
+        <v>420</v>
+      </c>
+      <c r="I58" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="10" t="str">
+        <v>916</v>
+      </c>
+      <c r="J58" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="12"/>
+        <v>524</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="10" t="str">
+      <c r="A59" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="9">
+        <v>360</v>
+      </c>
+      <c r="C59" s="9">
+        <v>25</v>
+      </c>
+      <c r="D59" s="9">
+        <v>220</v>
+      </c>
+      <c r="E59" s="9">
+        <v>30</v>
+      </c>
+      <c r="F59" s="9">
+        <v>0</v>
+      </c>
+      <c r="G59" s="9">
+        <v>0</v>
+      </c>
+      <c r="H59" s="9">
+        <v>400</v>
+      </c>
+      <c r="I59" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="str">
+        <v>1035</v>
+      </c>
+      <c r="J59" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="12"/>
+        <v>405</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N59" s="12" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30618"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80BA1352-2849-46D7-935F-B3439B196351}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F52B6DB-A955-40D1-A767-0CF02E3CB482}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -349,6 +349,36 @@
   </si>
   <si>
     <t>i am preparing for my mtt</t>
+  </si>
+  <si>
+    <t>Today is holdiay so I visited Amritsar Golden Temple and Wagha Border with my friend</t>
+  </si>
+  <si>
+    <t>After many days I goo to college and fells better</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I arrived at LPU law Gate </t>
+  </si>
+  <si>
+    <t>Today I am in train just using phone and enjoying the ride</t>
+  </si>
+  <si>
+    <t>I visited many places with my friends whom I meet after 2 month</t>
+  </si>
+  <si>
+    <t>I am just happy to spend time with my Parents</t>
+  </si>
+  <si>
+    <t>I am just worried about my Mid Term Exam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I am doing rest today </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I just visited market with my mother and buys clothes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I have spend my time while Wathching the movie  </t>
   </si>
 </sst>
 </file>
@@ -3597,247 +3627,511 @@
         <v>102</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="10" t="str">
+    <row r="60" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B60" s="9">
+        <v>420</v>
+      </c>
+      <c r="C60" s="9">
+        <v>30</v>
+      </c>
+      <c r="D60" s="9">
+        <v>90</v>
+      </c>
+      <c r="E60" s="9">
+        <v>120</v>
+      </c>
+      <c r="F60" s="9">
+        <v>0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9">
+        <v>300</v>
+      </c>
+      <c r="I60" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="10" t="str">
+        <v>960</v>
+      </c>
+      <c r="J60" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="12"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="10" t="str">
+        <v>480</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N60" s="12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A61" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="9">
+        <v>200</v>
+      </c>
+      <c r="C61" s="9">
+        <v>15</v>
+      </c>
+      <c r="D61" s="9">
+        <v>70</v>
+      </c>
+      <c r="E61" s="9">
+        <v>20</v>
+      </c>
+      <c r="F61" s="9">
+        <v>0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9">
+        <v>360</v>
+      </c>
+      <c r="I61" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="10" t="str">
+        <v>665</v>
+      </c>
+      <c r="J61" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="12"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="10" t="str">
+        <v>775</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N61" s="12" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A62" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="9">
+        <v>420</v>
+      </c>
+      <c r="C62" s="9">
+        <v>28</v>
+      </c>
+      <c r="D62" s="9">
+        <v>60</v>
+      </c>
+      <c r="E62" s="9">
+        <v>60</v>
+      </c>
+      <c r="F62" s="9">
+        <v>0</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9">
+        <v>280</v>
+      </c>
+      <c r="I62" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="10" t="str">
+        <v>848</v>
+      </c>
+      <c r="J62" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="12"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="10" t="str">
+        <v>592</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N62" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A63" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="9">
+        <v>300</v>
+      </c>
+      <c r="C63" s="9">
+        <v>40</v>
+      </c>
+      <c r="D63" s="9">
+        <v>90</v>
+      </c>
+      <c r="E63" s="9">
+        <v>30</v>
+      </c>
+      <c r="F63" s="9">
+        <v>0</v>
+      </c>
+      <c r="G63" s="9">
+        <v>0</v>
+      </c>
+      <c r="H63" s="9">
+        <v>400</v>
+      </c>
+      <c r="I63" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="10" t="str">
+        <v>860</v>
+      </c>
+      <c r="J63" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="12"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="10" t="str">
+        <v>580</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N63" s="12" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B64" s="9">
+        <v>250</v>
+      </c>
+      <c r="C64" s="9">
+        <v>20</v>
+      </c>
+      <c r="D64" s="9">
+        <v>200</v>
+      </c>
+      <c r="E64" s="9">
+        <v>40</v>
+      </c>
+      <c r="F64" s="9">
+        <v>0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>360</v>
+      </c>
+      <c r="I64" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="10" t="str">
+        <v>870</v>
+      </c>
+      <c r="J64" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="12"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="10" t="str">
+        <v>570</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N64" s="12" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A65" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="9">
+        <v>370</v>
+      </c>
+      <c r="C65" s="9">
+        <v>60</v>
+      </c>
+      <c r="D65" s="9">
+        <v>0</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>250</v>
+      </c>
+      <c r="I65" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="str">
+        <v>680</v>
+      </c>
+      <c r="J65" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="12"/>
+        <v>760</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N65" s="12" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
+      <c r="A66" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="9">
+        <v>320</v>
+      </c>
+      <c r="C66" s="9">
+        <v>20</v>
+      </c>
+      <c r="D66" s="9">
+        <v>0</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0</v>
+      </c>
+      <c r="F66" s="9">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>400</v>
+      </c>
+      <c r="I66" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
+        <v>740</v>
+      </c>
+      <c r="J66" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="12"/>
+        <v>700</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="10" t="str">
+      <c r="A67" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="9">
+        <v>300</v>
+      </c>
+      <c r="C67" s="9">
+        <v>15</v>
+      </c>
+      <c r="D67" s="9">
+        <v>120</v>
+      </c>
+      <c r="E67" s="9">
+        <v>30</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0</v>
+      </c>
+      <c r="H67" s="9">
+        <v>360</v>
+      </c>
+      <c r="I67" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="str">
+        <v>825</v>
+      </c>
+      <c r="J67" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="12"/>
+        <v>615</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N67" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
+      <c r="A68" s="8">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="9">
+        <v>280</v>
+      </c>
+      <c r="C68" s="9">
+        <v>10</v>
+      </c>
+      <c r="D68" s="9">
+        <v>320</v>
+      </c>
+      <c r="E68" s="9">
+        <v>30</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0</v>
+      </c>
+      <c r="G68" s="9">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
+        <v>260</v>
+      </c>
+      <c r="I68" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
+        <v>900</v>
+      </c>
+      <c r="J68" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="12"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
+        <v>540</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A69" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="9">
+        <v>300</v>
+      </c>
+      <c r="C69" s="9">
+        <v>120</v>
+      </c>
+      <c r="D69" s="9">
+        <v>300</v>
+      </c>
+      <c r="E69" s="9">
+        <v>120</v>
+      </c>
+      <c r="F69" s="9">
+        <v>250</v>
+      </c>
+      <c r="G69" s="9">
+        <v>5</v>
+      </c>
+      <c r="H69" s="9">
+        <v>300</v>
+      </c>
+      <c r="I69" s="10">
         <f t="shared" ref="I69:I132" si="2">IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J69" s="10">
         <f t="shared" ref="J69:J132" si="3">IF(I69="","",1440-I69)</f>
-        <v/>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="12"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
+        <v>50</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N69" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="9">
+        <v>540</v>
+      </c>
+      <c r="C70" s="9">
+        <v>20</v>
+      </c>
+      <c r="D70" s="9">
+        <v>0</v>
+      </c>
+      <c r="E70" s="9">
+        <v>0</v>
+      </c>
+      <c r="F70" s="9">
+        <v>0</v>
+      </c>
+      <c r="G70" s="9">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
+        <v>400</v>
+      </c>
+      <c r="I70" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
+        <v>960</v>
+      </c>
+      <c r="J70" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="12"/>
+        <v>480</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N70" s="12" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F52B6DB-A955-40D1-A767-0CF02E3CB482}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{439E77F5-B638-447E-A8B5-0422485E27EE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -379,6 +379,9 @@
   </si>
   <si>
     <t xml:space="preserve">Today I have spend my time while Wathching the movie  </t>
+  </si>
+  <si>
+    <t>Eng And Networking classs is off today because the teacher are in leave</t>
   </si>
 </sst>
 </file>
@@ -4133,27 +4136,51 @@
         <v>103</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
+    <row r="71" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="9">
+        <v>360</v>
+      </c>
+      <c r="C71" s="9">
+        <v>60</v>
+      </c>
+      <c r="D71" s="9">
+        <v>120</v>
+      </c>
+      <c r="E71" s="9">
+        <v>30</v>
+      </c>
+      <c r="F71" s="9">
+        <v>250</v>
+      </c>
+      <c r="G71" s="9">
+        <v>5</v>
+      </c>
+      <c r="H71" s="9">
+        <v>400</v>
+      </c>
+      <c r="I71" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J71" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="12"/>
+        <v>220</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N71" s="12" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30618"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{439E77F5-B638-447E-A8B5-0422485E27EE}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BC2CB64-07B2-4058-AAE3-E8FC78026838}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="120">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -382,6 +382,24 @@
   </si>
   <si>
     <t>Eng And Networking classs is off today because the teacher are in leave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today is Holiday </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today is Sunday we enjoy our days </t>
+  </si>
+  <si>
+    <t>all the classes are off because its Saturday</t>
+  </si>
+  <si>
+    <t>The 2 Classes are exempt Due Due to placement drive</t>
+  </si>
+  <si>
+    <t>Today feeling is good</t>
+  </si>
+  <si>
+    <t>We have to not attend Networking class</t>
   </si>
 </sst>
 </file>
@@ -4183,136 +4201,280 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
+      <c r="A72" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="9">
+        <v>220</v>
+      </c>
+      <c r="C72" s="9">
+        <v>70</v>
+      </c>
+      <c r="D72" s="9">
+        <v>100</v>
+      </c>
+      <c r="E72" s="9">
+        <v>50</v>
+      </c>
+      <c r="F72" s="9">
+        <v>200</v>
+      </c>
+      <c r="G72" s="9">
+        <v>4</v>
+      </c>
+      <c r="H72" s="9">
+        <v>360</v>
+      </c>
+      <c r="I72" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J72" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="12"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
+        <v>440</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N72" s="12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A73" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="9">
+        <v>410</v>
+      </c>
+      <c r="C73" s="9">
+        <v>60</v>
+      </c>
+      <c r="D73" s="9">
+        <v>250</v>
+      </c>
+      <c r="E73" s="9">
+        <v>40</v>
+      </c>
+      <c r="F73" s="9">
+        <v>200</v>
+      </c>
+      <c r="G73" s="9">
+        <v>4</v>
+      </c>
+      <c r="H73" s="9">
+        <v>280</v>
+      </c>
+      <c r="I73" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J73" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="12"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
+        <v>200</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N73" s="12" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="8">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="9">
+        <v>300</v>
+      </c>
+      <c r="C74" s="9">
+        <v>80</v>
+      </c>
+      <c r="D74" s="9">
+        <v>230</v>
+      </c>
+      <c r="E74" s="9">
+        <v>60</v>
+      </c>
+      <c r="F74" s="9">
+        <v>0</v>
+      </c>
+      <c r="G74" s="9">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9">
+        <v>320</v>
+      </c>
+      <c r="I74" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+        <v>990</v>
+      </c>
+      <c r="J74" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="12"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
+        <v>450</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N74" s="12" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A75" s="8">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="9">
+        <v>280</v>
+      </c>
+      <c r="C75" s="9">
+        <v>60</v>
+      </c>
+      <c r="D75" s="9">
+        <v>120</v>
+      </c>
+      <c r="E75" s="9">
+        <v>40</v>
+      </c>
+      <c r="F75" s="9">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>400</v>
+      </c>
+      <c r="I75" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+        <v>900</v>
+      </c>
+      <c r="J75" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="12"/>
+        <v>540</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
+      <c r="A76" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B76" s="9">
+        <v>320</v>
+      </c>
+      <c r="C76" s="9">
+        <v>60</v>
+      </c>
+      <c r="D76" s="9">
+        <v>100</v>
+      </c>
+      <c r="E76" s="9">
+        <v>30</v>
+      </c>
+      <c r="F76" s="9">
+        <v>0</v>
+      </c>
+      <c r="G76" s="9">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>280</v>
+      </c>
+      <c r="I76" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
+        <v>790</v>
+      </c>
+      <c r="J76" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="12"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
+        <v>650</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N76" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="9">
+        <v>260</v>
+      </c>
+      <c r="C77" s="9">
+        <v>60</v>
+      </c>
+      <c r="D77" s="9">
+        <v>120</v>
+      </c>
+      <c r="E77" s="9">
+        <v>45</v>
+      </c>
+      <c r="F77" s="9">
+        <v>100</v>
+      </c>
+      <c r="G77" s="9">
+        <v>2</v>
+      </c>
+      <c r="H77" s="9">
+        <v>240</v>
+      </c>
+      <c r="I77" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
+        <v>825</v>
+      </c>
+      <c r="J77" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="12"/>
+        <v>615</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="N77" s="12" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>

--- a/12605718.xlsx
+++ b/12605718.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srish\Desktop\GIT\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BC2CB64-07B2-4058-AAE3-E8FC78026838}"/>
+  <xr:revisionPtr revIDLastSave="177" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{813EAAAF-446D-4859-97ED-9551C0BD8837}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="120">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4477,47 +4477,91 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
+      <c r="A78" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="9">
+        <v>200</v>
+      </c>
+      <c r="C78" s="9">
+        <v>60</v>
+      </c>
+      <c r="D78" s="9">
+        <v>120</v>
+      </c>
+      <c r="E78" s="9">
+        <v>30</v>
+      </c>
+      <c r="F78" s="9">
+        <v>400</v>
+      </c>
+      <c r="G78" s="9">
+        <v>8</v>
+      </c>
+      <c r="H78" s="9">
+        <v>280</v>
+      </c>
+      <c r="I78" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J78" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
+        <v>350</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>49</v>
+      </c>
       <c r="N78" s="12"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
+      <c r="A79" s="8">
+        <v>46324</v>
+      </c>
+      <c r="B79" s="9">
+        <v>320</v>
+      </c>
+      <c r="C79" s="9">
+        <v>15</v>
+      </c>
+      <c r="D79" s="9">
+        <v>60</v>
+      </c>
+      <c r="E79" s="9">
+        <v>45</v>
+      </c>
+      <c r="F79" s="9">
+        <v>200</v>
+      </c>
+      <c r="G79" s="9">
+        <v>4</v>
+      </c>
+      <c r="H79" s="9">
+        <v>320</v>
+      </c>
+      <c r="I79" s="10">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+        <v>960</v>
+      </c>
+      <c r="J79" s="10">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
+        <v>480</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>49</v>
+      </c>
       <c r="N79" s="12"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
